--- a/セリフ編集/キャラタイプ別/標準×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×内気.xlsx
@@ -1849,7 +1849,7 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け……。よかったのか、どうなのか。</t>
+          <t xml:space="preserve">決着つかず……。よかったのか、どうなのか。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/標準×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×内気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -320,22 +320,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.standard.hit[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.shy[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.standard.hit[1]</t>
+          <t xml:space="preserve">atk.standard.shy[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -345,29 +345,29 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、立てます……あなたたちには、倒れたくなくて……。</t>
+          <t xml:space="preserve">あ、あの…いきますっ…!</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.standard.hit[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.shy[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.standard.hit[2]</t>
+          <t xml:space="preserve">atk.standard.shy[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -377,29 +377,29 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お願い、もう一回だけ……あそこには、負けたくないの……。</t>
+          <t xml:space="preserve">わ、わたし…まだまだ…!</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.standard.win[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.shy[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.standard.win[1]</t>
+          <t xml:space="preserve">atk.standard.shy[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -409,29 +409,29 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝っちゃった……。あの、私を切ったところに……信じられない……。</t>
+          <t xml:space="preserve">ま、負けたくないから…!</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.shy.standard.win[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.shy[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.standard.win[2]</t>
+          <t xml:space="preserve">atk.standard.shy[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -441,908 +441,3308 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちゃんと、戦えてましたか……? あそこの人に……。</t>
+          <t xml:space="preserve">こ、ここから…ですっ…!</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.lose[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.shy[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.lose[1]</t>
+          <t xml:space="preserve">bigmove.standard.shy[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けました。ごめんなさい。</t>
+          <t xml:space="preserve">あ、あの…いきます…！</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.lose[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.shy[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.lose[2]</t>
+          <t xml:space="preserve">bigmove.standard.shy[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言い出したの、わたしなのに……すみません。</t>
+          <t xml:space="preserve">こ、ここで…決めます…！</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.lose[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.shy[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.lose[3]</t>
+          <t xml:space="preserve">bigmove.standard.shy[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔、上げられないです。……ごめんなさい。</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.petition[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.shy[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.petition[1]</t>
+          <t xml:space="preserve">climax.standard.shy[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……社長。ひとつ、お願いが……。</t>
+          <t xml:space="preserve">（…ま、まだ…いけるはず…!）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.petition[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.shy[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.petition[2]</t>
+          <t xml:space="preserve">climax.standard.shy[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言うか迷ったんですけど……あの人と、やりたいです。</t>
+          <t xml:space="preserve">（こ、ここで…決めなきゃ…!）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.petition[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.petition[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わがままですよね。……でも、どうしても。</t>
+          <t xml:space="preserve">い、痛い…でも…まだ…</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.sendoff[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.sendoff[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ……ありがとうございます。行ってきます。</t>
+          <t xml:space="preserve">う、うぅ…でも…立てる…から…</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.sendoff[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.sendoff[2]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本当に、いいんですか……。嬉しいです。</t>
+          <t xml:space="preserve">ひっ…で、でも…負けたくない…</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.sendoff[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.shy.hit[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.sendoff[3]</t>
+          <t xml:space="preserve">standard.shy.hit[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。……頑張り、ます。</t>
+          <t xml:space="preserve">……まだ、立てます……あなたたちには、倒れたくなくて……。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.shy.hit[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.win[1]</t>
+          <t xml:space="preserve">standard.shy.hit[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……勝てました。</t>
+          <t xml:space="preserve">……お願い、もう一回だけ……あそこには、負けたくないの……。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.shy.win[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.win[2]</t>
+          <t xml:space="preserve">standard.shy.win[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……信じてもらえて、嬉しかったです。</t>
+          <t xml:space="preserve">……勝っちゃった……。あの、私を切ったところに……信じられない……。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.win[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.shy.win[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.win[3]</t>
+          <t xml:space="preserve">standard.shy.win[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……こんなこと、初めてです。</t>
+          <t xml:space="preserve">……ちゃんと、戦えてましたか……? あそこの人に……。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy._accept[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy._accept[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、わたし……? ……うん、逃げないよ。</t>
+          <t xml:space="preserve">う、動けない…</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy._accept[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy._accept[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名指しされるなんて、思ってなかった。……でも、受ける。</t>
+          <t xml:space="preserve">間に合わない…！</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy._accept[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy._accept[3]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自信、ないんだけど……。それでも、いいなら。</t>
+          <t xml:space="preserve">…ごめん…</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.draw[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.draw[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかず……。よかったのか、どうなのか。</t>
+          <t xml:space="preserve">さ、させない…！</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.draw[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.draw[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着、つかなかったね……。ちょっと、ほっとしてる。</t>
+          <t xml:space="preserve">ま、まだ…です…！</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.draw[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.draw[3]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……もう一度、やる? 今度は、ちゃんと。</t>
+          <t xml:space="preserve">だ、ダメ…！</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.lose[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.lose[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱり、わたしじゃ……だめだったね。</t>
+          <t xml:space="preserve">あ、合わせます…！</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.lose[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.lose[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">強かった……。何も、できなかった。</t>
+          <t xml:space="preserve">に、二人で…！</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.lose[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.lose[3]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。がっかり、させちゃったよね。</t>
+          <t xml:space="preserve">い、いっしょに…！</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.win[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.win[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ……勝っちゃった。ごめんなさい。</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.win[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.win[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしが勝ったんだよね……。まだ、信じられない。</t>
+          <t xml:space="preserve">こ、交代…します…</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.win[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_shy.win[3]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたのに……こんな結果で、よかったのかな。</t>
+          <t xml:space="preserve">い、行ってきます…！</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.shy.standard.high[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.standard.high[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ち越せて、嬉しいです</t>
+          <t xml:space="preserve">{partner}…ご、ごめん…私のせいで…</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.shy.standard.high[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.standard.high[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てて、よかった</t>
+          <t xml:space="preserve">つ、次は…絶対、{partner}を勝たせる…！</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.shy.standard.high[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.standard.high[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今夜、組の全員で受けて立ちます</t>
+          <t xml:space="preserve">{partner}…ほ、本当に…ありがとう…！</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.shy.standard.high[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">02 タッグマッチ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、私…頑張れた…{partner}のおかげ…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.lose[1]</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.lose[1]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けました。ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.lose[2]</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.lose[2]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">言い出したの、わたしなのに……すみません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.lose[3]</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.lose[3]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">顔、上げられないです。……ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.petition[1]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.petition[1]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの……社長。ひとつ、お願いが……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.petition[2]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.petition[2]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">言うか迷ったんですけど……あの人と、やりたいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.petition[3]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.petition[3]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わがままですよね。……でも、どうしても。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ……ありがとうございます。行ってきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本当に、いいんですか……。嬉しいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。……頑張り、ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.win[1]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.win[1]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの……勝てました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.win[2]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.win[2]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……信じてもらえて、嬉しかったです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_shy.win[3]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.win[3]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……こんなこと、初めてです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy._accept[1]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy._accept[1]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え、わたし……? ……うん、逃げないよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy._accept[2]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy._accept[2]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">名指しされるなんて、思ってなかった。……でも、受ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy._accept[3]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy._accept[3]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">自信、ないんだけど……。それでも、いいなら。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.draw[1]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.draw[1]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着つかず……。よかったのか、どうなのか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.draw[2]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.draw[2]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着、つかなかったね……。ちょっと、ほっとしてる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.draw[3]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.draw[3]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの……もう一度、やる? 今度は、ちゃんと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.lose[1]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.lose[1]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やっぱり、わたしじゃ……だめだったね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.lose[2]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.lose[2]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">強かった……。何も、できなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.lose[3]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.lose[3]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい。がっかり、させちゃったよね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.win[1]</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.win[1]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ……勝っちゃった。ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.win[2]</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.win[2]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしが勝ったんだよね……。まだ、信じられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_shy.win[3]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_shy.win[3]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">選んでくれたのに……こんな結果で、よかったのかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、その、私たちのメンバーのこと、お願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、あの、次のメイン…私たちに、お願いできませんか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、その、待遇の件で…一度、聞いてもらえますか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、その、私たちのこと、見てくれてますか…?</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あの…ありがとうございます。…うれしい、です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あの…ありがとう、ございます。みんなに、伝えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…そう、ですよね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あの、ありがとう…ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あの…ありがとうございます。…がんばります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ごめんなさい…次は、声、かけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ごめんなさい、控えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ごめんなさい…明日から、出ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…休ませて、もらいます…ありがとう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…大丈夫、です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ごめんなさい、注意します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（…俯いて、何も言わなかった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ごめんなさい、加減します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.attack.standard</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.attack.standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの…もう、一緒には…いられなくて</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.defend.standard</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy.defend.standard</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…やるしか、ないんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr" s="2">
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい、わたしのせいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝ち越せて、嬉しいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝てて、よかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……はい</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今夜、組の全員で受けて立ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">shy.standard.high[1]</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr" s="3">
+      <c r="D103" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……はい。受けて、立ちます</t>
         </is>
       </c>
     </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.shy.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい、わたしのせいで</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.shy.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……すみません</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ほんとうに、勝てるなんて</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……わたし、勝ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy.high[1]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けません。今日は</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H33"/>
+  <autoFilter ref="A1:H108"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×内気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H388"/>
+  <dimension ref="A1:H390"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -345,7 +345,7 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…いきますっ…!</t>
+          <t xml:space="preserve">あ、あの…いきますっ…！</t>
         </is>
       </c>
     </row>
@@ -377,7 +377,7 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたし…まだまだ…!</t>
+          <t xml:space="preserve">わ、わたし…まだまだ…！</t>
         </is>
       </c>
     </row>
@@ -409,7 +409,7 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けたくないから…!</t>
+          <t xml:space="preserve">ま、負けたくないから…！</t>
         </is>
       </c>
     </row>
@@ -441,7 +441,7 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、ここから…ですっ…!</t>
+          <t xml:space="preserve">こ、ここから…ですっ…！</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…ま、まだ…いけるはず…!）</t>
+          <t xml:space="preserve">（…ま、まだ…いけるはず…！）</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（こ、ここで…決めなきゃ…!）</t>
+          <t xml:space="preserve">（こ、ここで…決めなきゃ…！）</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちゃんと、戦えてましたか……? あそこの人に……。</t>
+          <t xml:space="preserve">……ちゃんと、戦えてましたか……？ あそこの人に……。</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、わたし……? ……うん、逃げないよ。</t>
+          <t xml:space="preserve">え、わたし……？ ……うん、逃げないよ。</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……もう一度、やる? 今度は、ちゃんと。</t>
+          <t xml:space="preserve">あの……もう一度、やる？ 今度は、ちゃんと。</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、その、私たちのこと、見てくれてますか…?</t>
+          <t xml:space="preserve">…社長、その、私たちのこと、見てくれてますか…？</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">な、なんだか今日、体が軽くて…!やれそうです…!</t>
+          <t xml:space="preserve">な、なんだか今日、体が軽くて…！やれそうです…！</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.shy[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6813,14 +6813,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんなすごい試合にわたしが…。相手が引き出してくれたんです</t>
+          <t xml:space="preserve">仲間がつないでくれたから、最後まで戦えました。</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">bestMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンって…まだ慣れなくて。でもベルトが重い分、逃げちゃいけないって…</t>
+          <t xml:space="preserve">あんなすごい試合にわたしが…。相手が引き出してくれたんです</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6877,14 +6877,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなわたしが殿堂に…。でも…ここに立てて…嬉しい。本当に嬉しいです</t>
+          <t xml:space="preserve">チャンピオンって…まだ慣れなくて。でもベルトが重い分、逃げちゃいけないって…</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.shy[1]</t>
+          <t xml:space="preserve">hallOfFame.standard.shy[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6909,14 +6909,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ありがとうございます…嬉しいです…</t>
+          <t xml:space="preserve">こんなわたしが殿堂に…。でも…ここに立てて…嬉しい。本当に嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.shy[2]</t>
+          <t xml:space="preserve">mediaAward.standard.shy[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6941,14 +6941,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな私でよかったんでしょうか…</t>
+          <t xml:space="preserve">あ、あの…ありがとうございます…嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.shy[1]</t>
+          <t xml:space="preserve">mediaAward.standard.shy[2]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPなんて…周りの人が強くしてくれただけで…。でも、嬉しいです</t>
+          <t xml:space="preserve">こんな私でよかったんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.shy[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.shy[1]</t>
+          <t xml:space="preserve">mvp.standard.shy[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ…わたし、ですか…？ 間違いじゃ…あ、ありがとうございます…</t>
+          <t xml:space="preserve">MVPなんて…周りの人が強くしてくれただけで…。でも、嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.shy[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">rookie.standard.shy[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの…ドームに、来られて、嬉しいです…</t>
+          <t xml:space="preserve">えっ…わたし、ですか…？ 間違いじゃ…あ、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">springTagChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…緊張します…でも、頑張ります…</t>
+          <t xml:space="preserve">相棒がいてくれたから、最後まで前を向けました。</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…皆さんのおかげ、です</t>
+          <t xml:space="preserve">…あ、あの…ドームに、来られて、嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、満員…ですか? …嘘みたい…</t>
+          <t xml:space="preserve">…緊張します…でも、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…皆さん、来てくださって、本当に嬉しいです…</t>
+          <t xml:space="preserve">…皆さんのおかげ、です</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、ございました…</t>
+          <t xml:space="preserve">…ま、満員…ですか？ …嘘みたい…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7214,29 +7214,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…ちょっとだけ、練習が楽しくなってきました…</t>
+          <t xml:space="preserve">…皆さん、来てくださって、本当に嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7246,29 +7246,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…みんなと一緒にいられて…嬉しいです…</t>
+          <t xml:space="preserve">…ありがとう、ございました…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.shy[1]</t>
+          <t xml:space="preserve">N1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7293,14 +7293,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…無理はしてないつもりなんですけど……少し休んだ方がいいかも…</t>
+          <t xml:space="preserve">あの…ちょっとだけ、練習が楽しくなってきました…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.shy[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.shy[1]</t>
+          <t xml:space="preserve">N2.standard.shy[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、あの…私なんかを応援してくれる人がいるなんて…</t>
+          <t xml:space="preserve">あの…みんなと一緒にいられて…嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.shy[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.shy[1]</t>
+          <t xml:space="preserve">N3.standard.shy[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…もう…わかりません…</t>
+          <t xml:space="preserve">あの…無理はしてないつもりなんですけど……少し休んだ方がいいかも…</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.shy[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.shy[1]</t>
+          <t xml:space="preserve">N4.standard.shy[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの……なんでもない、です…</t>
+          <t xml:space="preserve">え、あの…私なんかを応援してくれる人がいるなんて…</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.shy[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7406,29 +7406,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.shy[1]</t>
+          <t xml:space="preserve">N5_low.standard.shy[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ…ありがとう、ございます…（また…？）</t>
+          <t xml:space="preserve">…ごめんなさい…もう…わかりません…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.shy[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7438,29 +7438,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.shy[1]</t>
+          <t xml:space="preserve">N5_warning.standard.shy[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…あの…ありがとう、ございます…！</t>
+          <t xml:space="preserve">…あ、あの……なんでもない、です…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.shy[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.shy[1]</t>
+          <t xml:space="preserve">bonus_repeat.standard.shy[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、合宿…！ が、頑張ります…！</t>
+          <t xml:space="preserve">あ…ありがとう、ございます…（また…？）</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.shy[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.shy[1]</t>
+          <t xml:space="preserve">bonus.standard.shy[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7517,14 +7517,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと…見てくれてたんですか…？ わ、私…頑張ります…！</t>
+          <t xml:space="preserve">え…あの…ありがとう、ございます…！</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.shy[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.shy[1]</t>
+          <t xml:space="preserve">camp.standard.shy[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声をかけてもらえて…嬉しかったです…頑張ります…</t>
+          <t xml:space="preserve">が、合宿…！ が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.shy[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.shy[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.shy[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの、わたし……はい、わかりました</t>
+          <t xml:space="preserve">ずっと…見てくれてたんですか…？ わ、私…頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.shy[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.shy[2]</t>
+          <t xml:space="preserve">encourage.standard.shy[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7613,14 +7613,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。うまく、言えなくて</t>
+          <t xml:space="preserve">…声をかけてもらえて…嬉しかったです…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.shy[1]</t>
+          <t xml:space="preserve">faction_decree.standard.shy[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…テレビ…？ き、緊張します…で、でも頑張ります…！</t>
+          <t xml:space="preserve">……あの、わたし……はい、わかりました</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.shy[1]</t>
+          <t xml:space="preserve">faction_decree.standard.shy[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…楽しかった、です…（隅で小さく笑っている）</t>
+          <t xml:space="preserve">……ごめんなさい。うまく、言えなくて</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.shy[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.shy[1]</t>
+          <t xml:space="preserve">media.standard.shy[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…休んでいいんですか…？ ありがとうございます…</t>
+          <t xml:space="preserve">え…テレビ…？ き、緊張します…で、でも頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.shy[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.shy[1]</t>
+          <t xml:space="preserve">party.standard.shy[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7741,14 +7741,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…ご迷惑をおかけして…必ず、戻ります…</t>
+          <t xml:space="preserve">あ、あの…楽しかった、です…（隅で小さく笑っている）</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.shy[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.shy[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.shy[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">せ、専属の先生…！が、頑張ります…！</t>
+          <t xml:space="preserve">あの…休んでいいんですか…？ ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.shy[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.shy[1]</t>
+          <t xml:space="preserve">special_treatment.standard.shy[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…テレビ…？ わ、私なんかが…で、でもやってみたいです…</t>
+          <t xml:space="preserve">すみません…ご迷惑をおかけして…必ず、戻ります…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.shy[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.shy[1]</t>
+          <t xml:space="preserve">trainer.standard.shy[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…他の団体から…その…どうしたらいいか分からなくて…</t>
+          <t xml:space="preserve">せ、専属の先生…！が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.shy[1]</t>
+          <t xml:space="preserve">E1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…タイトルマッチ…挑戦させてもらえませんか…？</t>
+          <t xml:space="preserve">え…テレビ…？ わ、私なんかが…で、でもやってみたいです…</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.shy[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.shy[1]</t>
+          <t xml:space="preserve">E6.standard.shy[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7901,14 +7901,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…あの人と…試合させてもらえませんか…</t>
+          <t xml:space="preserve">あの…他の団体から…その…どうしたらいいか分からなくて…</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.shy[1]</t>
+          <t xml:space="preserve">S1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…すみません…体が…少し休ませてもらえますか…</t>
+          <t xml:space="preserve">あ、あの…タイトルマッチ…挑戦させてもらえませんか…？</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.shy[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.shy[1]</t>
+          <t xml:space="preserve">S2.standard.shy[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの…ごめんなさい…でも…このままだと…</t>
+          <t xml:space="preserve">あの…あの人と…試合させてもらえませんか…</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.shy[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.shy[1]</t>
+          <t xml:space="preserve">S3.standard.shy[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7997,14 +7997,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（目を逸らして、何も言えずにいる）</t>
+          <t xml:space="preserve">あの…すみません…体が…少し休ませてもらえますか…</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.shy[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.shy[1]</t>
+          <t xml:space="preserve">S4_direct.standard.shy[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…特訓…させてもらえませんか…？ もっと強くなりたいんです…</t>
+          <t xml:space="preserve">…あの…ごめんなさい…でも…このままだと…</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.shy[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.shy[1]</t>
+          <t xml:space="preserve">S4_silent.standard.shy[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…私でよければ…後輩の子たちに…何か伝えられたら…</t>
+          <t xml:space="preserve">…………（目を逸らして、何も言えずにいる）</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.shy[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.shy[1]</t>
+          <t xml:space="preserve">S5.standard.shy[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…!せ、精一杯やります…!</t>
+          <t xml:space="preserve">あの…特訓…させてもらえませんか…？ もっと強くなりたいんです…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.shy[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.shy[1]</t>
+          <t xml:space="preserve">S6.standard.shy[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、わ、わたしが…!? が、頑張ります……!</t>
+          <t xml:space="preserve">あの…私でよければ…後輩の子たちに…何か伝えられたら…</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.shy[1]</t>
+          <t xml:space="preserve">E1.accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ご迷惑を…早く治します…</t>
+          <t xml:space="preserve">は、はい…！せ、精一杯やります…！</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.shy[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.shy[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.shy[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…あの人のこと…もう…どうしたらいいか…</t>
+          <t xml:space="preserve">えっ、わ、わたしが…！？ が、頑張ります……！</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.shy[1]</t>
+          <t xml:space="preserve">B1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私が悪いんでしょうか…（不安そうに）</t>
+          <t xml:space="preserve">す、すみません…ご迷惑を…早く治します…</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.shy[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がコラボ…？ 本当に私でいいんですか…</t>
+          <t xml:space="preserve">あの…あの人のこと…もう…どうしたらいいか…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.shy[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.shy[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.shy[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がCMに…？ ほ、本当に大丈夫ですか…？</t>
+          <t xml:space="preserve">…私が悪いんでしょうか…（不安そうに）</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.shy[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.shy[1]</t>
+          <t xml:space="preserve">B4_brand.standard.shy[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フ、ファンの方に直接会うんですか…！ 緊張しますが頑張ります</t>
+          <t xml:space="preserve">わ、私がコラボ…？ 本当に私でいいんですか…</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.shy[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.shy[1]</t>
+          <t xml:space="preserve">B4_cm.standard.shy[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フ、ファッションショー…みんなに見られるんですよね…！</t>
+          <t xml:space="preserve">わ、私がCMに…？ ほ、本当に大丈夫ですか…？</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.shy[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.shy[1]</t>
+          <t xml:space="preserve">B4_fan.standard.shy[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…グラビア…？ は、恥ずかしいです…でも、やります…</t>
+          <t xml:space="preserve">フ、ファンの方に直接会うんですか…！ 緊張しますが頑張ります</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.shy[1]</t>
+          <t xml:space="preserve">B4_fashion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8413,14 +8413,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バ、バラエティ…しゃべるの…？ が、頑張ります…</t>
+          <t xml:space="preserve">フ、ファッションショー…みんなに見られるんですよね…！</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.shy[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.shy[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.shy[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私なんかでいいんですか…？ が、頑張ります…！</t>
+          <t xml:space="preserve">え…グラビア…？ は、恥ずかしいです…でも、やります…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.shy[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8462,29 +8462,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">B4_variety.standard.shy[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
+          <t xml:space="preserve">バ、バラエティ…しゃべるの…？ が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.shy[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8494,29 +8494,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">B4.standard.shy[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
+          <t xml:space="preserve">え…わ、私なんかでいいんですか…？ が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
+          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8573,14 +8573,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8605,14 +8605,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
+          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8637,14 +8637,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
+          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
@@ -8669,14 +8669,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…痛いです…</t>
+          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
+          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8765,14 +8765,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わったのに…どうして、また気になるんだろう…</t>
+          <t xml:space="preserve">う、うぅ…痛いです…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8797,14 +8797,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの日敗北した屈辱を…まだ、毎晩思い出すんです…</t>
+          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.shy[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.shy[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.shy[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8829,14 +8829,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
+          <t xml:space="preserve">…もう終わったのに…どうして、また気になるんだろう…</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.shy[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.shy[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.shy[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
+          <t xml:space="preserve">…あの日敗北した屈辱を…まだ、毎晩思い出すんです…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.shy[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.shy[2]</t>
+          <t xml:space="preserve">draftInterest.standard.shy[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
+          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.shy[3]</t>
+          <t xml:space="preserve">draftJoin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">draftJoin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8957,14 +8957,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[3]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">draftJoin.standard.shy[3]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8989,14 +8989,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.shy[1]</t>
+          <t xml:space="preserve">faGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
+          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.shy[1]</t>
+          <t xml:space="preserve">faGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9053,14 +9053,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
+          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.shy[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.shy[1]</t>
+          <t xml:space="preserve">faSigning.standard.shy[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9085,14 +9085,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">な、なんだか今日、体が軽くて…!やれそうです…!</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.shy[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.shy[1]</t>
+          <t xml:space="preserve">faWelcome.standard.shy[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
+          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.shy[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.shy[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.shy[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9149,14 +9149,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
+          <t xml:space="preserve">な、なんだか今日、体が軽くて…！やれそうです…！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.shy[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.shy[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.shy[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
+          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.shy[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.shy[2]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.shy[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9213,14 +9213,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…痛いです…</t>
+          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.shy[3]</t>
+          <t xml:space="preserve">injury.standard.shy[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9245,14 +9245,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
+          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.shy[1]</t>
+          <t xml:space="preserve">injury.standard.shy[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9277,14 +9277,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
+          <t xml:space="preserve">う、うぅ…痛いです…</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[3]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.shy[2]</t>
+          <t xml:space="preserve">injury.standard.shy[3]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
+          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.shy[3]</t>
+          <t xml:space="preserve">release.standard.shy[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9341,14 +9341,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お、お世話になりました…</t>
+          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">release.standard.shy[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9373,14 +9373,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
+          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[3]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">release.standard.shy[3]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+          <t xml:space="preserve">…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">rentalGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9437,14 +9437,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
+          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.shy[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
+          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.shy[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
+          <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.shy[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
+          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.shy[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.shy[1]</t>
+          <t xml:space="preserve">titleDefense.standard.shy[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
+          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">titleLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
+          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">titleWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
+          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お、お世話になりました…</t>
+          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9693,14 +9693,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
+          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
+          <t xml:space="preserve">…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
+          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
@@ -9789,14 +9789,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
+          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
@@ -9821,14 +9821,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
+          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9838,29 +9838,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.shy.standard[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しい…</t>
+          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9870,29 +9870,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.standard[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…目を合わせるのが怖い…私、何かしちゃったのかな…</t>
+          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.standard[2]</t>
+          <t xml:space="preserve">bond_39_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9917,14 +9917,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人の態度が…前と違う…私のせい…だよね…</t>
+          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しい…</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.shy.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9949,14 +9949,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人のそばだと…少しだけ自分でいられる気がする…</t>
+          <t xml:space="preserve">最近…目を合わせるのが怖い…私、何かしちゃったのかな…</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.shy.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9981,14 +9981,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…この人とだけは…普通に話せるようになってきた…かも</t>
+          <t xml:space="preserve">あの人の態度が…前と違う…私のせい…だよね…</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10013,14 +10013,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人がいなかったら…私、とっくにダメになってたと思う…</t>
+          <t xml:space="preserve">この人のそばだと…少しだけ自分でいられる気がする…</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人が隣にいるだけで…なんでも頑張れる気がするんです…</t>
+          <t xml:space="preserve">最近…この人とだけは…普通に話せるようになってきた…かも</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10077,14 +10077,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…あの人のこと、前ほど気にならなくなった…かも</t>
+          <t xml:space="preserve">この人がいなかったら…私、とっくにダメになってたと思う…</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10109,14 +10109,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの頃のピリピリした感じ…もうないかな…</t>
+          <t xml:space="preserve">あの人が隣にいるだけで…なんでも頑張れる気がするんです…</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10141,14 +10141,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人のこと…考えると胸がきゅってなる…負けたくない…</t>
+          <t xml:space="preserve">最近…あの人のこと、前ほど気にならなくなった…かも</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習してるのを見かけると…自分も走り出したくなる…</t>
+          <t xml:space="preserve">あの頃のピリピリした感じ…もうないかな…</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人にだけは…絶対に負けたくない…今はそれだけ…</t>
+          <t xml:space="preserve">あの人のこと…考えると胸がきゅってなる…負けたくない…</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖い…けど、逃げたらもっと後悔する…だから…</t>
+          <t xml:space="preserve">練習してるのを見かけると…自分も走り出したくなる…</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人がいなかったら…今の私はいない。それだけは…わかる</t>
+          <t xml:space="preserve">あの人にだけは…絶対に負けたくない…今はそれだけ…</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げたい…でも…この人からだけは逃げちゃダメ…</t>
+          <t xml:space="preserve">怖い…けど、逃げたらもっと後悔する…だから…</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.standard[1]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいんだ…って…最近やっと思えるようになりました…</t>
+          <t xml:space="preserve">この人がいなかったら…今の私はいない。それだけは…わかる</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.standard[2]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10365,14 +10365,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に来れて…よかった…心からそう思います…</t>
+          <t xml:space="preserve">逃げたい…でも…この人からだけは逃げちゃダメ…</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.shy.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.shy.standard[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…無理…ここにいちゃいけない気がする……</t>
+          <t xml:space="preserve">ここにいていいんだ…って…最近やっと思えるようになりました…</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.shy.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.shy.standard[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここに私の居場所なんて…あるのかな……</t>
+          <t xml:space="preserve">この団体に来れて…よかった…心からそう思います…</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.standard[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.shy[1]</t>
+          <t xml:space="preserve">trust_below_20.shy.standard[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったけど…精一杯やれました…</t>
+          <t xml:space="preserve">…もう…無理…ここにいちゃいけない気がする……</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.standard[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.shy[2]</t>
+          <t xml:space="preserve">trust_below_35.shy.standard[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10493,14 +10493,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…いい試合だったって…思いたいです</t>
+          <t xml:space="preserve">…ここに私の居場所なんて…あるのかな……</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すごい試合ができました…！ 信じられない…！</t>
+          <t xml:space="preserve">負けちゃったけど…精一杯やれました…</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.shy[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.shy[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10557,14 +10557,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…しかもいい試合で…夢みたい…</t>
+          <t xml:space="preserve">悔しいけど…いい試合だったって…思いたいです</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10589,14 +10589,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う…また負けちゃった…ごめんなさい…</t>
+          <t xml:space="preserve">す、すごい試合ができました…！ 信じられない…！</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.shy[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10621,14 +10621,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私…ダメですよね…ごめんなさい…</t>
+          <t xml:space="preserve">勝てた…しかもいい試合で…夢みたい…</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10653,14 +10653,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…！ よかった…</t>
+          <t xml:space="preserve">う…また負けちゃった…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.shy[2]</t>
+          <t xml:space="preserve">GL-01.loss.standard.shy[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…勝てて本当に嬉しいです…</t>
+          <t xml:space="preserve">私…ダメですよね…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.shy[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10717,14 +10717,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、えっと…もう少し頑張ります…</t>
+          <t xml:space="preserve">か、勝てた…！ よかった…</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.shy[2]</t>
+          <t xml:space="preserve">GL-01.win.standard.shy[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10749,14 +10749,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の練習…うまくできてるかな…</t>
+          <t xml:space="preserve">嬉しい…勝てて本当に嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.shy[1]</t>
+          <t xml:space="preserve">GL-02.standard.shy[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10781,14 +10781,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私…ちゃんとやれてますか…？ 不安です…</t>
+          <t xml:space="preserve">あ、えっと…もう少し頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.shy[1]</t>
+          <t xml:space="preserve">GL-02.standard.shy[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10813,14 +10813,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ここにいていいんですね…嬉しいです…</t>
+          <t xml:space="preserve">今日の練習…うまくできてるかな…</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.shy[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.shy[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.shy[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10845,14 +10845,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">近くにいてくれると…安心する…</t>
+          <t xml:space="preserve">私…ちゃんとやれてますか…？ 不安です…</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.shy[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.shy[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.shy[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10877,14 +10877,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すごいな…私も頑張らなきゃ…</t>
+          <t xml:space="preserve">あ、あの…ここにいていいんですね…嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.shy[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.shy[1]</t>
+          <t xml:space="preserve">GL-04.standard.shy[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10909,14 +10909,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出られなかった…私じゃダメなんですか…</t>
+          <t xml:space="preserve">近くにいてくれると…安心する…</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.shy[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.shy[2]</t>
+          <t xml:space="preserve">GL-05.standard.shy[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10941,14 +10941,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…次は…出してもらえますか…？</t>
+          <t xml:space="preserve">…すごいな…私も頑張らなきゃ…</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.shy[1]</t>
+          <t xml:space="preserve">GL-06.standard.shy[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10973,14 +10973,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が…重くて…すみません…迷惑かけて…</t>
+          <t xml:space="preserve">出られなかった…私じゃダメなんですか…</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.shy[1]</t>
+          <t xml:space="preserve">GL-06.standard.shy[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11005,14 +11005,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私…足引っ張ってますよね…ごめんなさい…</t>
+          <t xml:space="preserve">あの…次は…出してもらえますか…？</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.shy[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.shy[2]</t>
+          <t xml:space="preserve">GL-07.standard.shy[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11037,14 +11037,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てない…勝てない…どうしたらいいの…</t>
+          <t xml:space="preserve">体が…重くて…すみません…迷惑かけて…</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.shy[1]</t>
+          <t xml:space="preserve">GL-08.standard.shy[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11069,14 +11069,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝…嘘みたい…でも自信になってます…！</t>
+          <t xml:space="preserve">わ、私…足引っ張ってますよね…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.shy[1]</t>
+          <t xml:space="preserve">GL-08.standard.shy[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11101,14 +11101,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなに置いてかれちゃう…怖い…</t>
+          <t xml:space="preserve">勝てない…勝てない…どうしたらいいの…</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.shy[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.shy[2]</t>
+          <t xml:space="preserve">GL-09.standard.shy[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11133,14 +11133,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我…早く治って…お願い…</t>
+          <t xml:space="preserve">連勝…嘘みたい…でも自信になってます…！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">GL-10.standard.shy[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11165,14 +11165,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ…なんか、普通に戻っちゃった…かな</t>
+          <t xml:space="preserve">みんなに置いてかれちゃう…怖い…</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">GL-10.standard.shy[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11197,14 +11197,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すごく調子よかったのに…でも、いい思い出です…</t>
+          <t xml:space="preserve">怪我…早く治って…お願い…</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11214,29 +11214,29 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたなんて…。身体は痛いけど、最後まで、逃げたくない</t>
+          <t xml:space="preserve">あ…なんか、普通に戻っちゃった…かな</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11246,29 +11246,29 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…。でも、みんなが繋いでくれたから、私が締めなきゃ</t>
+          <t xml:space="preserve">すごく調子よかったのに…でも、いい思い出です…</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11293,14 +11293,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つ、相手が来る…。怖い、けど…ここで逃げたら、繋げないから</t>
+          <t xml:space="preserve">ここまで来られたなんて…。身体は痛いけど、最後まで、逃げたくない</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11325,14 +11325,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…でも、私の番だから。行かなきゃ</t>
+          <t xml:space="preserve">足が震えてる…。でも、みんなが繋いでくれたから、私が締めなきゃ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.shy[1]</t>
+          <t xml:space="preserve">preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11357,14 +11357,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人…倒せた…! はぁ、はぁ…怖いけど、まだ退かない…! 次の人、来て…!</t>
+          <t xml:space="preserve">あ、相手が来る…。怖い、けど…ここで逃げたら、繋げないから</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.shy[2]</t>
+          <t xml:space="preserve">preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11389,14 +11389,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…でも、まだ立ってる。ここは、渡せないから…次、来て</t>
+          <t xml:space="preserve">足が震えてる…でも、私の番だから。行かなきゃ</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11406,12 +11406,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">survivor.standard.shy[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11421,14 +11421,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がMVPでいいのかな……でも、二人がつないでくれたから、ここに立てました</t>
+          <t xml:space="preserve">一人…倒せた…！ はぁ、はぁ…怖いけど、まだ退かない…！ 次の人、来て…！</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[2]</t>
+          <t xml:space="preserve">survivor.standard.shy[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11453,14 +11453,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">み、みんなで勝てて……ほんとに嬉しい。私なんかがここに立ってていいのかな</t>
+          <t xml:space="preserve">足が震えてる…でも、まだ立ってる。ここは、渡せないから…次、来て</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[3]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11485,14 +11485,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てたこと、それが一番嬉しいです。MVPは……二人のおかげです</t>
+          <t xml:space="preserve">わ、私がMVPでいいのかな……でも、二人がつないでくれたから、ここに立てました</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11517,14 +11517,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでもらえたのは嬉しいです。でも……みんなで勝ちたかった。次こそは</t>
+          <t xml:space="preserve">み、みんなで勝てて……ほんとに嬉しい。私なんかがここに立ってていいのかな</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[3]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[2]</t>
+          <t xml:space="preserve">champion.standard.shy[3]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11549,14 +11549,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP……嬉しいけど、胸を張れない。次は仲間と一緒に笑いたい</t>
+          <t xml:space="preserve">三人で勝てたこと、それが一番嬉しいです。MVPは……二人のおかげです</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[3]</t>
+          <t xml:space="preserve">defiant.standard.shy[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11581,14 +11581,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな賞をもらっても……みんなが悔しい顔してるのに、喜べないです</t>
+          <t xml:space="preserve">選んでもらえたのは嬉しいです。でも……みんなで勝ちたかった。次こそは</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[1]</t>
+          <t xml:space="preserve">defiant.standard.shy[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11613,14 +11613,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、怖かったです。でも……次の相手が来ても、逃げたくなかったんです</t>
+          <t xml:space="preserve">MVP……嬉しいけど、胸を張れない。次は仲間と一緒に笑いたい</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[3]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[2]</t>
+          <t xml:space="preserve">defiant.standard.shy[3]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11645,14 +11645,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">手が震えてます。でも、最後まで立ててよかった……</t>
+          <t xml:space="preserve">こんな賞をもらっても……みんなが悔しい顔してるのに、喜べないです</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[3]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11677,14 +11677,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来るかわからなくて怖かったけど……気づいたら、最後の一人でした</t>
+          <t xml:space="preserve">こ、怖かったです。でも……次の相手が来ても、逃げたくなかったんです</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[2]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[2]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11709,14 +11709,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じられない…。でも…嬉しい…！</t>
+          <t xml:space="preserve">手が震えてます。でも、最後まで立ててよかった……</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[3]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[2]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[3]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11741,14 +11741,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしが優勝…？ 夢じゃないよね…</t>
+          <t xml:space="preserve">何人来るかわからなくて怖かったけど……気づいたら、最後の一人でした</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11773,14 +11773,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…。もっと頑張らないと…</t>
+          <t xml:space="preserve">信じられない…。でも…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.shy[2]</t>
+          <t xml:space="preserve">champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11805,14 +11805,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱり…わたしなんか…。でも…諦めない…</t>
+          <t xml:space="preserve">わ、わたしが優勝…？ 夢じゃないよね…</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.shy[1]</t>
+          <t xml:space="preserve">postLose.standard.shy[1]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11837,14 +11837,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…よかった…</t>
+          <t xml:space="preserve">ご、ごめんなさい…。もっと頑張らないと…</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[2]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.shy[2]</t>
+          <t xml:space="preserve">postLose.standard.shy[2]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11869,14 +11869,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…終わりじゃないんだ…頑張る</t>
+          <t xml:space="preserve">やっぱり…わたしなんか…。でも…諦めない…</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.shy[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11901,14 +11901,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張れた…かな。もっと強くなりたい…</t>
+          <t xml:space="preserve">か、勝てた…よかった…</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.shy[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11933,14 +11933,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと戦えて…嬉しかった…</t>
+          <t xml:space="preserve">まだ…終わりじゃないんだ…頑張る</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">postWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11965,14 +11965,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">震えてるのは…きっと、嬉しいからだと思う</t>
+          <t xml:space="preserve">が、頑張れた…かな。もっと強くなりたい…</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">postWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11997,14 +11997,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのが信じられない…でも、負けたくない</t>
+          <t xml:space="preserve">みんなと戦えて…嬉しかった…</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12029,14 +12029,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張する…でも、逃げない</t>
+          <t xml:space="preserve">震えてるのは…きっと、嬉しいからだと思う</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12061,14 +12061,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張ります…！</t>
+          <t xml:space="preserve">ここまで来れたのが信じられない…でも、負けたくない</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.shy[1]</t>
+          <t xml:space="preserve">preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12093,14 +12093,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、私が…？ …頑張らなきゃ</t>
+          <t xml:space="preserve">緊張する…でも、逃げない</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.shy[2]</t>
+          <t xml:space="preserve">preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12125,14 +12125,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、嘘…？ わ、私でいいんですか…？</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12142,12 +12142,12 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">summon.standard.shy[1]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12157,14 +12157,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張ります…！</t>
+          <t xml:space="preserve">え、私が…？ …頑張らなきゃ</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[2]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">summon.standard.shy[2]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -12189,14 +12189,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…信じられない…夢、みたい…</t>
+          <t xml:space="preserve">う、嘘…？ わ、私でいいんですか…？</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
@@ -12221,14 +12221,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…対抗戦を…お願いしたくて…</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12253,14 +12253,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、でも…負けるつもりはないです…</t>
+          <t xml:space="preserve">か、勝てました…信じられない…夢、みたい…</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="12">
@@ -12285,14 +12285,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そ、そうですか…残念です…</t>
+          <t xml:space="preserve">あ、あの…対抗戦を…お願いしたくて…</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[2]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="12">
@@ -12317,14 +12317,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、でも…いつかきっと…</t>
+          <t xml:space="preserve">で、でも…負けるつもりはないです…</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[1]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12334,12 +12334,12 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12349,14 +12349,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…私が…もっと頑張れていれば…</t>
+          <t xml:space="preserve">そ、そうですか…残念です…</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[2]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12381,14 +12381,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でも…次こそ…</t>
+          <t xml:space="preserve">で、でも…いつかきっと…</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[1]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.shy[1]</t>
+          <t xml:space="preserve">result_lose.standard.shy[1]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12413,14 +12413,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…。みんなのおかげです…</t>
+          <t xml:space="preserve">ごめんなさい…私が…もっと頑張れていれば…</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[2]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.shy[2]</t>
+          <t xml:space="preserve">result_lose.standard.shy[2]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12445,14 +12445,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほっとしました…。よかった…</t>
+          <t xml:space="preserve">悔しい…でも…次こそ…</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">result_win.standard.shy[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12477,14 +12477,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…！ み、みんなの看板、汚さずに済んだ…よかった…</t>
+          <t xml:space="preserve">か、勝てた…。みんなのおかげです…</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[2]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12494,12 +12494,12 @@
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">result_win.standard.shy[2]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12509,14 +12509,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私でも…団体の役に立てたのかな…</t>
+          <t xml:space="preserve">ほっとしました…。よかった…</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12541,14 +12541,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、嬉しい…みんなと一緒に戦えて…勝てて…</t>
+          <t xml:space="preserve">か、勝てた…！ み、みんなの看板、汚さずに済んだ…よかった…</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12558,29 +12558,29 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなに幸せなことがあっていいのかな…</t>
+          <t xml:space="preserve">わ、私でも…団体の役に立てたのかな…</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12590,29 +12590,29 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+          <t xml:space="preserve">う、嬉しい…みんなと一緒に戦えて…勝てて…</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.shy[1]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12622,29 +12622,29 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">fighter.standard.shy[1]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+          <t xml:space="preserve">こ、こんなに幸せなことがあっていいのかな…</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="12">
@@ -12669,44 +12669,108 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="40" customHeight="1">
+      <c r="A389" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="40" customHeight="1">
+      <c r="A390" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[2]</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr" s="2">
+      <c r="B390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr" s="12">
+      <c r="D390" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr" s="2">
+      <c r="E390" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr" s="3">
+      <c r="F390" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H388"/>
+  <autoFilter ref="A1:H390"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×内気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H390"/>
+  <dimension ref="A1:H397"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4224,7 +4224,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.standard.shy[1]</t>
+          <t xml:space="preserve">decline_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…い、いいんですか…？ あ、ありがとうございます…！ 頑張ります…！</t>
+          <t xml:space="preserve">は、はい……それで、大丈夫です。あの、リングに上がれるなら、わたしはそれで……。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.standard.shy[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.standard.shy[1]</t>
+          <t xml:space="preserve">decline_hold.standard.shy[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4281,14 +4281,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そ、それだけでも…ありがたいです…。ありがとうございます……。</t>
+          <t xml:space="preserve">え……そ、そのままで、いいんですか……？ わ、わたし……っ、ごめんなさい、涙が……。ありがとうございます……！</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.standard.shy[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.standard.shy[1]</t>
+          <t xml:space="preserve">decline_open.standard.shy[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4313,14 +4313,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう…ですか……。す、すみません、変なこと言って……。</t>
+          <t xml:space="preserve">あ……あの、はい……。わ、わたし、最近ついていけてないなって、思ってたので……。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.standard.shy[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.standard.shy[1]</t>
+          <t xml:space="preserve">decline_strict.standard.shy[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…社長…。{tenure}その…言いにくいんですけど…お給料のこと…少しだけ……。</t>
+          <t xml:space="preserve">……っ、は、はい……。あの、分かり、ました……。すみません、今日は、これで……。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.shy[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.standard.shy[2]</t>
+          <t xml:space="preserve">decline_voluntary_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4377,14 +4377,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…す、すみません社長…。{record}もう少しだけ…お願いできたらなって……。</t>
+          <t xml:space="preserve">はい……。あの、ちゃんと聞いてくれて、うれしかったです。…わたし、まだ辞めませんから。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.standard.shy[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.standard.shy[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.standard.shy[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……は、はい…分かりました……。す、すみませんでした……。</t>
+          <t xml:space="preserve">そ、そんな……わたしが、お願いした、のに……。…はい、…はい。ありがとう、ございます……！</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.standard.shy[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.standard.shy[1]</t>
+          <t xml:space="preserve">decline_voluntary_open.standard.shy[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの、辞め……辞めさせてください……。もう、無理なんです……。</t>
+          <t xml:space="preserve">あの……わ、わたしから、お願いが……。お給料、下げてください。見合って、ない気がするので……。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.shy[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.standard.shy[2]</t>
+          <t xml:space="preserve">raise_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。もう、ここにはいられません……。</t>
+          <t xml:space="preserve">え…い、いいんですか…？ あ、ありがとうございます…！ 頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.standard.shy[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…聞いてくれるんですか…？ {record}あの…私…ここにいていいのか、分からなくなって……。</t>
+          <t xml:space="preserve">そ、それだけでも…ありがたいです…。ありがとうございます……。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.standard.shy[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.standard.shy[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.standard.shy[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…社長……。{tenure}す、すみません…ここを…離れたいんです……。</t>
+          <t xml:space="preserve">……そう…ですか……。す、すみません、変なこと言って……。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.shy[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.shy[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.standard.shy[2]</t>
+          <t xml:space="preserve">raise_open.standard.shy[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい……。{tenure}私には…ここにいる資格がないような気がして……。</t>
+          <t xml:space="preserve">あ、あの…社長…。{tenure}その…言いにくいんですけど…お給料のこと…少しだけ……。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.shy[2]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.standard.shy[1]</t>
+          <t xml:space="preserve">raise_open.standard.shy[2]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4601,14 +4601,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、ありがとうございました…。{tenure_farewell}{rivalry}…お世話になりました……。</t>
+          <t xml:space="preserve">…す、すみません社長…。{record}もう少しだけ…お願いできたらなって……。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.standard.shy[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.standard.shy[1]</t>
+          <t xml:space="preserve">raise_refuse.standard.shy[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご、ごめんなさい……。でも…もう、決めたんです……。</t>
+          <t xml:space="preserve">……は、はい…分かりました……。す、すみませんでした……。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.standard.shy[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.shy[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.standard.shy[1]</t>
+          <t xml:space="preserve">sudden_departure.standard.shy[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4665,370 +4665,370 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…そ、そこまでしてくれるんですか…？ ……あの…もう少しだけ…頑張ります……。</t>
+          <t xml:space="preserve">……あの、辞め……辞めさせてください……。もう、無理なんです……。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい。もう、ここにはいられません……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え…聞いてくれるんですか…？ {record}あの…私…ここにいていいのか、分からなくなって……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの…社長……。{tenure}す、すみません…ここを…離れたいんです……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ごめんなさい……。{tenure}私には…ここにいる資格がないような気がして……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あ、ありがとうございました…。{tenure_farewell}{rivalry}…お世話になりました……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご、ごめんなさい……。でも…もう、決めたんです……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え…そ、そこまでしてくれるんですか…？ ……あの…もう少しだけ…頑張ります……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.standard.shy[1]</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr" s="2">
+      <c r="B145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr" s="12">
+      <c r="D145" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.standard.shy[1]</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr" s="2">
+      <c r="E145" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr" s="3">
+      <c r="F145" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">え…でも、今の仲間を置いていくなんて…
 ごめんなさい、どうしても首を縦に振れないです</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="40" customHeight="1">
-      <c r="A139" t="inlineStr" s="15">
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.standard.shy[1]</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr" s="2">
+      <c r="B146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr" s="12">
+      <c r="D146" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.standard.shy[1]</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr" s="2">
+      <c r="E146" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr" s="3">
+      <c r="F146" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">まだここで学ぶことがあるんです…。
 …すみません</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="40" customHeight="1">
-      <c r="A140" t="inlineStr" s="15">
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.standard.shy[1]</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr" s="2">
+      <c r="B147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr" s="12">
+      <c r="D147" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.standard.shy[1]</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr" s="2">
+      <c r="E147" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr" s="3">
+      <c r="F147" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">え…私なんかでいいんですか…？
 …ちょっと考えさせてください</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="40" customHeight="1">
-      <c r="A141" t="inlineStr" s="15">
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.standard.shy[1]</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr" s="2">
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr" s="12">
+      <c r="D148" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.standard.shy[1]</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr" s="2">
+      <c r="E148" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr" s="3">
+      <c r="F148" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">期待に応えられるよう、頑張ります…！
 …必ず、成長してみせます</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="40" customHeight="1">
-      <c r="A142" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、その、私たちのメンバーのこと、お願いします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="40" customHeight="1">
-      <c r="A143" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、あの、次のメイン…私たちに、お願いできませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="40" customHeight="1">
-      <c r="A144" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、その、待遇の件で…一度、聞いてもらえますか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="40" customHeight="1">
-      <c r="A145" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、その、私たちのこと、見てくれてますか…？</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="40" customHeight="1">
-      <c r="A146" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…あの…ありがとうございます。…うれしい、です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="40" customHeight="1">
-      <c r="A147" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="40" customHeight="1">
-      <c r="A148" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.shy[1]</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
-        </is>
-      </c>
-    </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.shy[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.shy[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、ありがとうございます。</t>
+          <t xml:space="preserve">…社長、その、私たちのメンバーのこと、お願いします。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.shy[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.shy[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5085,14 +5085,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…わかりました。</t>
+          <t xml:space="preserve">…社長、あの、次のメイン…私たちに、お願いできませんか。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.shy[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.shy[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5117,14 +5117,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、ありがとうございます。</t>
+          <t xml:space="preserve">…社長、その、待遇の件で…一度、聞いてもらえますか。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.shy[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.shy[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.shy[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの…ありがとう、ございます。みんなに、伝えます。</t>
+          <t xml:space="preserve">…社長、その、私たちのこと、見てくれてますか…？</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5181,14 +5181,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…そう、ですよね。</t>
+          <t xml:space="preserve">…あの…ありがとうございます。…うれしい、です。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの、ありがとう…ございます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの…ありがとうございます。…がんばります。</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5277,14 +5277,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとうございます。</t>
+          <t xml:space="preserve">…はい…わかりました。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…次は、声、かけます。</t>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+          <t xml:space="preserve">…あの…ありがとう、ございます。みんなに、伝えます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5405,14 +5405,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…はい…そう、ですよね。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5437,14 +5437,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…。</t>
+          <t xml:space="preserve">…あの、ありがとう…ございます。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5469,14 +5469,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、控えます。</t>
+          <t xml:space="preserve">…あの…ありがとうございます。…がんばります。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…明日から、出ます。</t>
+          <t xml:space="preserve">…はい…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5565,14 +5565,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+          <t xml:space="preserve">…ごめんなさい…次は、声、かけます。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5604,7 +5604,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5629,14 +5629,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…休ませて、もらいます…ありがとう。</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5661,14 +5661,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…大丈夫、です。</t>
+          <t xml:space="preserve">…はい…。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5693,14 +5693,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい、控えます。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5725,14 +5725,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、注意します。</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…。</t>
+          <t xml:space="preserve">…ごめんなさい…明日から、出ます。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5796,7 +5796,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい。</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…俯いて、何も言わなかった）</t>
+          <t xml:space="preserve">…はい…休ませて、もらいます…ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+          <t xml:space="preserve">…はい…大丈夫、です。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ごめんなさい、加減します。</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+          <t xml:space="preserve">…はい…ごめんなさい、注意します。</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.shy[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.shy[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
+          <t xml:space="preserve">…はい…。</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.shy.attack.standard</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.attack.standard</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6013,14 +6013,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…もう、一緒には…いられなくて</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.shy.defend.standard</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.defend.standard</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6045,29 +6045,29 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるしか、ないんです</t>
+          <t xml:space="preserve">…はい…ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6077,29 +6077,29 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい、わたしのせいです</t>
+          <t xml:space="preserve">（…俯いて、何も言わなかった）</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6109,29 +6109,29 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ち越せて、嬉しいです</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.shy[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6141,29 +6141,29 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい</t>
+          <t xml:space="preserve">…はい…ごめんなさい、加減します。</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.shy[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6173,29 +6173,29 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てて、よかった</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.shy[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6205,29 +6205,29 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい</t>
+          <t xml:space="preserve">…はい…ありがとう、ございます。</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.shy.high[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.attack.standard</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.high[1]</t>
+          <t xml:space="preserve">shy.attack.standard</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6237,29 +6237,29 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今夜、組の全員で受けて立ちます</t>
+          <t xml:space="preserve">あの…もう、一緒には…いられなくて</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.shy.high[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.shy.defend.standard</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.high[1]</t>
+          <t xml:space="preserve">shy.defend.standard</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい。受けて、立ちます</t>
+          <t xml:space="preserve">…やるしか、ないんです</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.shy.hp_high[1]</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.hp_high[1]</t>
+          <t xml:space="preserve">standard.shy.high[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい、わたしのせいで</t>
+          <t xml:space="preserve">……ごめんなさい、わたしのせいです</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.shy.hp_mid[1]</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy.hp_mid[1]</t>
+          <t xml:space="preserve">standard.shy.high[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6333,14 +6333,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません</t>
+          <t xml:space="preserve">……勝ち越せて、嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
@@ -6365,14 +6365,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ほんとうに、勝てるなんて</t>
+          <t xml:space="preserve">……ごめんなさい</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わたし、勝ちます</t>
+          <t xml:space="preserve">……勝てて、よかった</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.shy.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
@@ -6429,238 +6429,238 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けません。今日は</t>
+          <t xml:space="preserve">……はい</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy.high[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わたし、こんなに動けたんですか…？</t>
+          <t xml:space="preserve">……今夜、組の全員で受けて立ちます</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.standard.shy[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy.high[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">な、なんだか今日、体が軽くて…！やれそうです…！</t>
+          <t xml:space="preserve">……はい。受けて、立ちます</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.standard.shy[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.shy.hp_high[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy.hp_high[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
+          <t xml:space="preserve">……ごめんなさい、わたしのせいで</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.standard.shy[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.shy.hp_mid[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy.hp_mid[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
+          <t xml:space="preserve">……すみません</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy.high[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がリングに立つ意味…あるんでしょうか…</t>
+          <t xml:space="preserve">……ほんとうに、勝てるなんて</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy.high[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ自信はないですけど…もう少しだけ、頑張ってみます</t>
+          <t xml:space="preserve">……わたし、勝ちます</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.shy.high[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy.high[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ不安ですけど…頑張りたいです</t>
+          <t xml:space="preserve">……負けません。今日は</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.standard.shy[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6685,14 +6685,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱり…私なんかじゃ、ダメなんでしょうか…</t>
+          <t xml:space="preserve">え…わたし、こんなに動けたんですか…？</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.standard.shy[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.standard.shy[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.standard.shy[1]</t>
+          <t xml:space="preserve">fresh.standard.shy[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治ったのに…また迷惑かけちゃうかも…</t>
+          <t xml:space="preserve">な、なんだか今日、体が軽くて…！やれそうです…！</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.standard.shy[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.standard.shy[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.standard.shy[1]</t>
+          <t xml:space="preserve">heavy.standard.shy[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6749,14 +6749,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戻ってこれたけど…また壊れたらって思うと…怖いです</t>
+          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.standard.shy[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.standard.shy[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.standard.shy[1]</t>
+          <t xml:space="preserve">warm.standard.shy[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったんですけど…また怪我したらって思うと…</t>
+          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.shy[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,29 +6798,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がつないでくれたから、最後まで戦えました。</t>
+          <t xml:space="preserve">私がリングに立つ意味…あるんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.shy[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6830,29 +6830,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんなすごい試合にわたしが…。相手が引き出してくれたんです</t>
+          <t xml:space="preserve">まだ自信はないですけど…もう少しだけ、頑張ってみます</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6862,29 +6862,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンって…まだ慣れなくて。でもベルトが重い分、逃げちゃいけないって…</t>
+          <t xml:space="preserve">まだ不安ですけど…頑張りたいです</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.shy[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.standard.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6894,29 +6894,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.shy[1]</t>
+          <t xml:space="preserve">defeat.standard.shy[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなわたしが殿堂に…。でも…ここに立てて…嬉しい。本当に嬉しいです</t>
+          <t xml:space="preserve">やっぱり…私なんかじゃ、ダメなんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.standard.shy[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6926,29 +6926,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.shy[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.standard.shy[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ありがとうございます…嬉しいです…</t>
+          <t xml:space="preserve">体は治ったのに…また迷惑かけちゃうかも…</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.standard.shy[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6958,29 +6958,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.shy[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.standard.shy[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな私でよかったんでしょうか…</t>
+          <t xml:space="preserve">戻ってこれたけど…また壊れたらって思うと…怖いです</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.shy[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.standard.shy[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6990,29 +6990,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.shy[1]</t>
+          <t xml:space="preserve">penalty_end.standard.shy[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPなんて…周りの人が強くしてくれただけで…。でも、嬉しいです</t>
+          <t xml:space="preserve">怪我は治ったんですけど…また怪我したらって思うと…</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.shy[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ…わたし、ですか…？ 間違いじゃ…あ、ありがとうございます…</t>
+          <t xml:space="preserve">仲間がつないでくれたから、最後まで戦えました。</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.standard.shy[1]</t>
+          <t xml:space="preserve">bestMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒がいてくれたから、最後まで前を向けました。</t>
+          <t xml:space="preserve">あんなすごい試合にわたしが…。相手が引き出してくれたんです</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの…ドームに、来られて、嬉しいです…</t>
+          <t xml:space="preserve">チャンピオンって…まだ慣れなくて。でもベルトが重い分、逃げちゃいけないって…</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.shy[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">hallOfFame.standard.shy[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…緊張します…でも、頑張ります…</t>
+          <t xml:space="preserve">こんなわたしが殿堂に…。でも…ここに立てて…嬉しい。本当に嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">mediaAward.standard.shy[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…皆さんのおかげ、です</t>
+          <t xml:space="preserve">あ、あの…ありがとうございます…嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.shy[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">mediaAward.standard.shy[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、満員…ですか？ …嘘みたい…</t>
+          <t xml:space="preserve">こんな私でよかったんでしょうか…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.shy[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">mvp.standard.shy[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…皆さん、来てくださって、本当に嬉しいです…</t>
+          <t xml:space="preserve">MVPなんて…周りの人が強くしてくれただけで…。でも、嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.shy[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">rookie.standard.shy[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7261,14 +7261,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、ございました…</t>
+          <t xml:space="preserve">えっ…わたし、ですか…？ 間違いじゃ…あ、ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.shy[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7278,29 +7278,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.shy[1]</t>
+          <t xml:space="preserve">springTagChampion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…ちょっとだけ、練習が楽しくなってきました…</t>
+          <t xml:space="preserve">相棒がいてくれたから、最後まで前を向けました。</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7310,29 +7310,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…みんなと一緒にいられて…嬉しいです…</t>
+          <t xml:space="preserve">…あ、あの…ドームに、来られて、嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7342,29 +7342,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…無理はしてないつもりなんですけど……少し休んだ方がいいかも…</t>
+          <t xml:space="preserve">…緊張します…でも、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、あの…私なんかを応援してくれる人がいるなんて…</t>
+          <t xml:space="preserve">…皆さんのおかげ、です</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7406,29 +7406,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…もう…わかりません…</t>
+          <t xml:space="preserve">…ま、満員…ですか？ …嘘みたい…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7438,29 +7438,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あ、あの……なんでもない、です…</t>
+          <t xml:space="preserve">…皆さん、来てくださって、本当に嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.shy[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7470,29 +7470,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ…ありがとう、ございます…（また…？）</t>
+          <t xml:space="preserve">…ありがとう、ございました…</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7502,29 +7502,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.shy[1]</t>
+          <t xml:space="preserve">N1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…あの…ありがとう、ございます…！</t>
+          <t xml:space="preserve">あの…ちょっとだけ、練習が楽しくなってきました…</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.shy[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7534,29 +7534,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.shy[1]</t>
+          <t xml:space="preserve">N2.standard.shy[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、合宿…！ が、頑張ります…！</t>
+          <t xml:space="preserve">あの…みんなと一緒にいられて…嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.shy[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7566,29 +7566,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.shy[1]</t>
+          <t xml:space="preserve">N3.standard.shy[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと…見てくれてたんですか…？ わ、私…頑張ります…！</t>
+          <t xml:space="preserve">あの…無理はしてないつもりなんですけど……少し休んだ方がいいかも…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.shy[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7598,29 +7598,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.shy[1]</t>
+          <t xml:space="preserve">N4.standard.shy[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声をかけてもらえて…嬉しかったです…頑張ります…</t>
+          <t xml:space="preserve">え、あの…私なんかを応援してくれる人がいるなんて…</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.shy[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7630,29 +7630,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.shy[1]</t>
+          <t xml:space="preserve">N5_low.standard.shy[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの、わたし……はい、わかりました</t>
+          <t xml:space="preserve">…ごめんなさい…もう…わかりません…</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.shy[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7662,29 +7662,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.shy[2]</t>
+          <t xml:space="preserve">N5_warning.standard.shy[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。うまく、言えなくて</t>
+          <t xml:space="preserve">…あ、あの……なんでもない、です…</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.shy[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.shy[1]</t>
+          <t xml:space="preserve">bonus_repeat.standard.shy[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…テレビ…？ き、緊張します…で、でも頑張ります…！</t>
+          <t xml:space="preserve">あ…ありがとう、ございます…（また…？）</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.shy[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.shy[1]</t>
+          <t xml:space="preserve">bonus.standard.shy[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7741,14 +7741,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…楽しかった、です…（隅で小さく笑っている）</t>
+          <t xml:space="preserve">え…あの…ありがとう、ございます…！</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.shy[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.shy[1]</t>
+          <t xml:space="preserve">camp.standard.shy[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…休んでいいんですか…？ ありがとうございます…</t>
+          <t xml:space="preserve">が、合宿…！ が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.shy[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.shy[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.shy[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…ご迷惑をおかけして…必ず、戻ります…</t>
+          <t xml:space="preserve">ずっと…見てくれてたんですか…？ わ、私…頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.shy[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.shy[1]</t>
+          <t xml:space="preserve">encourage.standard.shy[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">せ、専属の先生…！が、頑張ります…！</t>
+          <t xml:space="preserve">…声をかけてもらえて…嬉しかったです…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.shy[1]</t>
+          <t xml:space="preserve">faction_decree.standard.shy[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…テレビ…？ わ、私なんかが…で、でもやってみたいです…</t>
+          <t xml:space="preserve">……あの、わたし……はい、わかりました</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.shy[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.shy[1]</t>
+          <t xml:space="preserve">faction_decree.standard.shy[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7901,14 +7901,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…他の団体から…その…どうしたらいいか分からなくて…</t>
+          <t xml:space="preserve">……ごめんなさい。うまく、言えなくて</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.shy[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.shy[1]</t>
+          <t xml:space="preserve">media.standard.shy[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…タイトルマッチ…挑戦させてもらえませんか…？</t>
+          <t xml:space="preserve">え…テレビ…？ き、緊張します…で、でも頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.shy[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.shy[1]</t>
+          <t xml:space="preserve">party.standard.shy[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…あの人と…試合させてもらえませんか…</t>
+          <t xml:space="preserve">あ、あの…楽しかった、です…（隅で小さく笑っている）</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.shy[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.shy[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.shy[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7997,14 +7997,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…すみません…体が…少し休ませてもらえますか…</t>
+          <t xml:space="preserve">あの…休んでいいんですか…？ ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.shy[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.shy[1]</t>
+          <t xml:space="preserve">special_treatment.standard.shy[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの…ごめんなさい…でも…このままだと…</t>
+          <t xml:space="preserve">すみません…ご迷惑をおかけして…必ず、戻ります…</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.shy[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.shy[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.shy[1]</t>
+          <t xml:space="preserve">trainer.standard.shy[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（目を逸らして、何も言えずにいる）</t>
+          <t xml:space="preserve">せ、専属の先生…！が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.shy[1]</t>
+          <t xml:space="preserve">E1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…特訓…させてもらえませんか…？ もっと強くなりたいんです…</t>
+          <t xml:space="preserve">え…テレビ…？ わ、私なんかが…で、でもやってみたいです…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.shy[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.shy[1]</t>
+          <t xml:space="preserve">E6.standard.shy[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…私でよければ…後輩の子たちに…何か伝えられたら…</t>
+          <t xml:space="preserve">あの…他の団体から…その…どうしたらいいか分からなくて…</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.shy[1]</t>
+          <t xml:space="preserve">S1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は、はい…！せ、精一杯やります…！</t>
+          <t xml:space="preserve">あ、あの…タイトルマッチ…挑戦させてもらえませんか…？</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.shy[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.shy[1]</t>
+          <t xml:space="preserve">S2.standard.shy[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、わ、わたしが…！？ が、頑張ります……！</t>
+          <t xml:space="preserve">あの…あの人と…試合させてもらえませんか…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.shy[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.shy[1]</t>
+          <t xml:space="preserve">S3.standard.shy[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ご迷惑を…早く治します…</t>
+          <t xml:space="preserve">あの…すみません…体が…少し休ませてもらえますか…</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.shy[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.shy[1]</t>
+          <t xml:space="preserve">S4_direct.standard.shy[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…あの人のこと…もう…どうしたらいいか…</t>
+          <t xml:space="preserve">…あの…ごめんなさい…でも…このままだと…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.shy[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.shy[1]</t>
+          <t xml:space="preserve">S4_silent.standard.shy[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私が悪いんでしょうか…（不安そうに）</t>
+          <t xml:space="preserve">…………（目を逸らして、何も言えずにいる）</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.shy[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.shy[1]</t>
+          <t xml:space="preserve">S5.standard.shy[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がコラボ…？ 本当に私でいいんですか…</t>
+          <t xml:space="preserve">あの…特訓…させてもらえませんか…？ もっと強くなりたいんです…</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.shy[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.shy[1]</t>
+          <t xml:space="preserve">S6.standard.shy[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がCMに…？ ほ、本当に大丈夫ですか…？</t>
+          <t xml:space="preserve">あの…私でよければ…後輩の子たちに…何か伝えられたら…</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.shy[1]</t>
+          <t xml:space="preserve">E1.accept.standard.shy[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フ、ファンの方に直接会うんですか…！ 緊張しますが頑張ります</t>
+          <t xml:space="preserve">は、はい…！せ、精一杯やります…！</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.shy[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.shy[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.shy[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.shy[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8413,14 +8413,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フ、ファッションショー…みんなに見られるんですよね…！</t>
+          <t xml:space="preserve">えっ、わ、わたしが…！？ が、頑張ります……！</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.shy[1]</t>
+          <t xml:space="preserve">B1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…グラビア…？ は、恥ずかしいです…でも、やります…</t>
+          <t xml:space="preserve">す、すみません…ご迷惑を…早く治します…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.shy[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.shy[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.shy[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バ、バラエティ…しゃべるの…？ が、頑張ります…</t>
+          <t xml:space="preserve">あの…あの人のこと…もう…どうしたらいいか…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.shy[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.shy[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.shy[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私なんかでいいんですか…？ が、頑張ります…！</t>
+          <t xml:space="preserve">…私が悪いんでしょうか…（不安そうに）</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.shy[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8526,29 +8526,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">B4_brand.standard.shy[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
+          <t xml:space="preserve">わ、私がコラボ…？ 本当に私でいいんですか…</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.shy[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8558,29 +8558,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">B4_cm.standard.shy[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
+          <t xml:space="preserve">わ、私がCMに…？ ほ、本当に大丈夫ですか…？</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.shy[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8590,29 +8590,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">B4_fan.standard.shy[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
+          <t xml:space="preserve">フ、ファンの方に直接会うんですか…！ 緊張しますが頑張ります</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8622,29 +8622,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">B4_fashion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
+          <t xml:space="preserve">フ、ファッションショー…みんなに見られるんですよね…！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.shy[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8654,29 +8654,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.shy[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
+          <t xml:space="preserve">え…グラビア…？ は、恥ずかしいです…でも、やります…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.shy[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8686,29 +8686,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">B4_variety.standard.shy[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
+          <t xml:space="preserve">バ、バラエティ…しゃべるの…？ が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.shy[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8718,29 +8718,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">B4.standard.shy[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
+          <t xml:space="preserve">え…わ、私なんかでいいんですか…？ が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8765,14 +8765,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…痛いです…</t>
+          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8797,14 +8797,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8829,14 +8829,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わったのに…どうして、また気になるんだろう…</t>
+          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの日敗北した屈辱を…まだ、毎晩思い出すんです…</t>
+          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
+          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8957,14 +8957,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
+          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8989,14 +8989,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
+          <t xml:space="preserve">う、うぅ…痛いです…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.shy[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.shy[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9053,14 +9053,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+          <t xml:space="preserve">…もう終わったのに…どうして、また気になるんだろう…</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.shy[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.shy[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.shy[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9085,14 +9085,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
+          <t xml:space="preserve">…あの日敗北した屈辱を…まだ、毎晩思い出すんです…</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.shy[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.shy[1]</t>
+          <t xml:space="preserve">draftInterest.standard.shy[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
+          <t xml:space="preserve">あ、あの…私なんかで良ければ…が、頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.shy[1]</t>
+          <t xml:space="preserve">draftJoin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9149,14 +9149,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">な、なんだか今日、体が軽くて…！やれそうです…！</t>
+          <t xml:space="preserve">あ、あの…よ、よろしくお願いします…！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.shy[1]</t>
+          <t xml:space="preserve">draftJoin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
+          <t xml:space="preserve">う、うぅ…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.shy[3]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.shy[1]</t>
+          <t xml:space="preserve">draftJoin.standard.shy[3]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9213,14 +9213,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
+          <t xml:space="preserve">…っ、よ、よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.shy[1]</t>
+          <t xml:space="preserve">faGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9245,14 +9245,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
+          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.shy[2]</t>
+          <t xml:space="preserve">faGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9277,14 +9277,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…痛いです…</t>
+          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.shy[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.shy[3]</t>
+          <t xml:space="preserve">faSigning.standard.shy[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
+          <t xml:space="preserve">あ、あの…よろしくお願いします…頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.shy[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.shy[1]</t>
+          <t xml:space="preserve">faWelcome.standard.shy[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9341,14 +9341,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
+          <t xml:space="preserve">よ、よろしくお願いします…が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.shy[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.shy[2]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.shy[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9373,14 +9373,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
+          <t xml:space="preserve">な、なんだか今日、体が軽くて…！やれそうです…！</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.shy[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.shy[3]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.shy[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お、お世話になりました…</t>
+          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.shy[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.shy[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9437,14 +9437,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
+          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.shy[1]</t>
+          <t xml:space="preserve">injury.standard.shy[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+          <t xml:space="preserve">ご、ごめんなさい…ちょっと休みます…</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.shy[2]</t>
+          <t xml:space="preserve">injury.standard.shy[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
+          <t xml:space="preserve">う、うぅ…痛いです…</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.shy[3]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.shy[1]</t>
+          <t xml:space="preserve">injury.standard.shy[3]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
+          <t xml:space="preserve">す、すみません…ご迷惑を…</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.shy[1]</t>
+          <t xml:space="preserve">release.standard.shy[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
+          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.shy[1]</t>
+          <t xml:space="preserve">release.standard.shy[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
+          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.shy[3]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.shy[1]</t>
+          <t xml:space="preserve">release.standard.shy[3]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
+          <t xml:space="preserve">…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">rentalGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
+          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">scoutGreeting.standard.shy[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9693,14 +9693,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
+          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">scoutGreeting.standard.shy[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お、お世話になりました…</t>
+          <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
+          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.shy[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">titleDefense.standard.shy[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9789,14 +9789,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
+          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">titleLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9821,14 +9821,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
+          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9838,12 +9838,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">titleWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9853,14 +9853,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
+          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
+          <t xml:space="preserve">ご、ごめんなさい…役に立てなくて…</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.standard[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9902,29 +9902,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.shy.standard[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しい…</t>
+          <t xml:space="preserve">す、すみません…ありがとうございました…</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9934,29 +9934,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.standard[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…目を合わせるのが怖い…私、何かしちゃったのかな…</t>
+          <t xml:space="preserve">…お、お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9966,29 +9966,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.shy.standard[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人の態度が…前と違う…私のせい…だよね…</t>
+          <t xml:space="preserve">あ、あの…短い間ですけど…よろしくお願いします…</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9998,29 +9998,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.shy.standard[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人のそばだと…少しだけ自分でいられる気がする…</t>
+          <t xml:space="preserve">…ごめんなさい…でも…諦めたくない…です…</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.shy.standard[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…この人とだけは…普通に話せるようになってきた…かも</t>
+          <t xml:space="preserve">よ、よかった…守れた…（ほっとしている）</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10062,29 +10062,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.standard[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人がいなかったら…私、とっくにダメになってたと思う…</t>
+          <t xml:space="preserve">…ごめんなさい…ベルト…守れなかった…</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10094,29 +10094,29 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.shy.standard[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人が隣にいるだけで…なんでも頑張れる気がするんです…</t>
+          <t xml:space="preserve">え…わ、私が…チャンピオン…？ 夢みたい…</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.standard[1]</t>
+          <t xml:space="preserve">bond_39_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10141,14 +10141,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…あの人のこと、前ほど気にならなくなった…かも</t>
+          <t xml:space="preserve">…もう…同じ部屋にいるだけで…苦しい…</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.shy.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの頃のピリピリした感じ…もうないかな…</t>
+          <t xml:space="preserve">最近…目を合わせるのが怖い…私、何かしちゃったのかな…</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人のこと…考えると胸がきゅってなる…負けたくない…</t>
+          <t xml:space="preserve">あの人の態度が…前と違う…私のせい…だよね…</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.shy.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習してるのを見かけると…自分も走り出したくなる…</t>
+          <t xml:space="preserve">この人のそばだと…少しだけ自分でいられる気がする…</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人にだけは…絶対に負けたくない…今はそれだけ…</t>
+          <t xml:space="preserve">最近…この人とだけは…普通に話せるようになってきた…かも</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.shy.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怖い…けど、逃げたらもっと後悔する…だから…</t>
+          <t xml:space="preserve">この人がいなかったら…私、とっくにダメになってたと思う…</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人がいなかったら…今の私はいない。それだけは…わかる</t>
+          <t xml:space="preserve">あの人が隣にいるだけで…なんでも頑張れる気がするんです…</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.shy.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.standard[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10365,14 +10365,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げたい…でも…この人からだけは逃げちゃダメ…</t>
+          <t xml:space="preserve">最近…あの人のこと、前ほど気にならなくなった…かも</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.shy.standard[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいんだ…って…最近やっと思えるようになりました…</t>
+          <t xml:space="preserve">あの頃のピリピリした感じ…もうないかな…</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.shy.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に来れて…よかった…心からそう思います…</t>
+          <t xml:space="preserve">あの人のこと…考えると胸がきゅってなる…負けたくない…</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.shy.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう…無理…ここにいちゃいけない気がする……</t>
+          <t xml:space="preserve">練習してるのを見かけると…自分も走り出したくなる…</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.shy.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10493,14 +10493,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここに私の居場所なんて…あるのかな……</t>
+          <t xml:space="preserve">あの人にだけは…絶対に負けたくない…今はそれだけ…</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.shy[1]</t>
+          <t xml:space="preserve">rivalry_50_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったけど…精一杯やれました…</t>
+          <t xml:space="preserve">怖い…けど、逃げたらもっと後悔する…だから…</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.shy[2]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.standard[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10557,14 +10557,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…いい試合だったって…思いたいです</t>
+          <t xml:space="preserve">この人がいなかったら…今の私はいない。それだけは…わかる</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.shy[1]</t>
+          <t xml:space="preserve">rivalry_70_up.shy.standard[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10589,14 +10589,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">す、すごい試合ができました…！ 信じられない…！</t>
+          <t xml:space="preserve">逃げたい…でも…この人からだけは逃げちゃダメ…</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.shy[2]</t>
+          <t xml:space="preserve">trust_above_75.shy.standard[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10621,14 +10621,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…しかもいい試合で…夢みたい…</t>
+          <t xml:space="preserve">ここにいていいんだ…って…最近やっと思えるようになりました…</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.shy.standard[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10638,12 +10638,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.shy[1]</t>
+          <t xml:space="preserve">trust_above_75.shy.standard[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10653,14 +10653,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う…また負けちゃった…ごめんなさい…</t>
+          <t xml:space="preserve">この団体に来れて…よかった…心からそう思います…</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.shy.standard[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.shy[2]</t>
+          <t xml:space="preserve">trust_below_20.shy.standard[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私…ダメですよね…ごめんなさい…</t>
+          <t xml:space="preserve">…もう…無理…ここにいちゃいけない気がする……</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.shy.standard[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.shy[1]</t>
+          <t xml:space="preserve">trust_below_35.shy.standard[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10717,14 +10717,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…！ よかった…</t>
+          <t xml:space="preserve">…ここに私の居場所なんて…あるのかな……</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.shy[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10749,14 +10749,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…勝てて本当に嬉しいです…</t>
+          <t xml:space="preserve">負けちゃったけど…精一杯やれました…</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.shy[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.shy[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10781,14 +10781,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、えっと…もう少し頑張ります…</t>
+          <t xml:space="preserve">悔しいけど…いい試合だったって…思いたいです</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.shy[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10813,14 +10813,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の練習…うまくできてるかな…</t>
+          <t xml:space="preserve">す、すごい試合ができました…！ 信じられない…！</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10845,14 +10845,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私…ちゃんとやれてますか…？ 不安です…</t>
+          <t xml:space="preserve">勝てた…しかもいい試合で…夢みたい…</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.shy[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10877,14 +10877,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ここにいていいんですね…嬉しいです…</t>
+          <t xml:space="preserve">う…また負けちゃった…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.shy[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.shy[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10909,14 +10909,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">近くにいてくれると…安心する…</t>
+          <t xml:space="preserve">私…ダメですよね…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.shy[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10941,14 +10941,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すごいな…私も頑張らなきゃ…</t>
+          <t xml:space="preserve">か、勝てた…！ よかった…</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.shy[2]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.shy[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.shy[2]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10973,14 +10973,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出られなかった…私じゃダメなんですか…</t>
+          <t xml:space="preserve">嬉しい…勝てて本当に嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.shy[2]</t>
+          <t xml:space="preserve">GL-02.standard.shy[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11005,14 +11005,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…次は…出してもらえますか…？</t>
+          <t xml:space="preserve">あ、えっと…もう少し頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.shy[1]</t>
+          <t xml:space="preserve">GL-02.standard.shy[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11037,14 +11037,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が…重くて…すみません…迷惑かけて…</t>
+          <t xml:space="preserve">今日の練習…うまくできてるかな…</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.shy[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.shy[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.shy[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11069,14 +11069,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私…足引っ張ってますよね…ごめんなさい…</t>
+          <t xml:space="preserve">私…ちゃんとやれてますか…？ 不安です…</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.shy[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.shy[2]</t>
+          <t xml:space="preserve">GL-03.up.standard.shy[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11101,14 +11101,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てない…勝てない…どうしたらいいの…</t>
+          <t xml:space="preserve">あ、あの…ここにいていいんですね…嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.shy[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.shy[1]</t>
+          <t xml:space="preserve">GL-04.standard.shy[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11133,14 +11133,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝…嘘みたい…でも自信になってます…！</t>
+          <t xml:space="preserve">近くにいてくれると…安心する…</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.shy[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.shy[1]</t>
+          <t xml:space="preserve">GL-05.standard.shy[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11165,14 +11165,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなに置いてかれちゃう…怖い…</t>
+          <t xml:space="preserve">…すごいな…私も頑張らなきゃ…</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.shy[2]</t>
+          <t xml:space="preserve">GL-06.standard.shy[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11197,14 +11197,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我…早く治って…お願い…</t>
+          <t xml:space="preserve">出られなかった…私じゃダメなんですか…</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[2]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">GL-06.standard.shy[2]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11229,14 +11229,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ…なんか、普通に戻っちゃった…かな</t>
+          <t xml:space="preserve">あの…次は…出してもらえますか…？</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.shy[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">GL-07.standard.shy[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11261,14 +11261,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すごく調子よかったのに…でも、いい思い出です…</t>
+          <t xml:space="preserve">体が…重くて…すみません…迷惑かけて…</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11278,29 +11278,29 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">GL-08.standard.shy[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたなんて…。身体は痛いけど、最後まで、逃げたくない</t>
+          <t xml:space="preserve">わ、私…足引っ張ってますよね…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11310,29 +11310,29 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">GL-08.standard.shy[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…。でも、みんなが繋いでくれたから、私が締めなきゃ</t>
+          <t xml:space="preserve">勝てない…勝てない…どうしたらいいの…</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.shy[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11342,29 +11342,29 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">GL-09.standard.shy[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、相手が来る…。怖い、けど…ここで逃げたら、繋げないから</t>
+          <t xml:space="preserve">連勝…嘘みたい…でも自信になってます…！</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11374,29 +11374,29 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">GL-10.standard.shy[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…でも、私の番だから。行かなきゃ</t>
+          <t xml:space="preserve">みんなに置いてかれちゃう…怖い…</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[2]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11406,29 +11406,29 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.shy[1]</t>
+          <t xml:space="preserve">GL-10.standard.shy[2]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人…倒せた…！ はぁ、はぁ…怖いけど、まだ退かない…！ 次の人、来て…！</t>
+          <t xml:space="preserve">怪我…早く治って…お願い…</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11438,29 +11438,29 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…でも、まだ立ってる。ここは、渡せないから…次、来て</t>
+          <t xml:space="preserve">あ…なんか、普通に戻っちゃった…かな</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11470,29 +11470,29 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がMVPでいいのかな……でも、二人がつないでくれたから、ここに立てました</t>
+          <t xml:space="preserve">すごく調子よかったのに…でも、いい思い出です…</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[2]</t>
+          <t xml:space="preserve">preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11517,14 +11517,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">み、みんなで勝てて……ほんとに嬉しい。私なんかがここに立ってていいのかな</t>
+          <t xml:space="preserve">ここまで来られたなんて…。身体は痛いけど、最後まで、逃げたくない</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[3]</t>
+          <t xml:space="preserve">preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11549,14 +11549,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てたこと、それが一番嬉しいです。MVPは……二人のおかげです</t>
+          <t xml:space="preserve">足が震えてる…。でも、みんなが繋いでくれたから、私が締めなきゃ</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[1]</t>
+          <t xml:space="preserve">preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11581,14 +11581,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでもらえたのは嬉しいです。でも……みんなで勝ちたかった。次こそは</t>
+          <t xml:space="preserve">あ、相手が来る…。怖い、けど…ここで逃げたら、繋げないから</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[2]</t>
+          <t xml:space="preserve">preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11613,14 +11613,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP……嬉しいけど、胸を張れない。次は仲間と一緒に笑いたい</t>
+          <t xml:space="preserve">足が震えてる…でも、私の番だから。行かなきゃ</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[3]</t>
+          <t xml:space="preserve">survivor.standard.shy[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11645,14 +11645,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな賞をもらっても……みんなが悔しい顔してるのに、喜べないです</t>
+          <t xml:space="preserve">一人…倒せた…！ はぁ、はぁ…怖いけど、まだ退かない…！ 次の人、来て…！</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[2]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[1]</t>
+          <t xml:space="preserve">survivor.standard.shy[2]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11677,14 +11677,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、怖かったです。でも……次の相手が来ても、逃げたくなかったんです</t>
+          <t xml:space="preserve">足が震えてる…でも、まだ立ってる。ここは、渡せないから…次、来て</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[2]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11709,14 +11709,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">手が震えてます。でも、最後まで立ててよかった……</t>
+          <t xml:space="preserve">わ、私がMVPでいいのかな……でも、二人がつないでくれたから、ここに立てました</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[3]</t>
+          <t xml:space="preserve">champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11741,14 +11741,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来るかわからなくて怖かったけど……気づいたら、最後の一人でした</t>
+          <t xml:space="preserve">み、みんなで勝てて……ほんとに嬉しい。私なんかがここに立ってていいのかな</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[3]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[3]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11773,14 +11773,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じられない…。でも…嬉しい…！</t>
+          <t xml:space="preserve">三人で勝てたこと、それが一番嬉しいです。MVPは……二人のおかげです</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11790,12 +11790,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[2]</t>
+          <t xml:space="preserve">defiant.standard.shy[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11805,14 +11805,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしが優勝…？ 夢じゃないよね…</t>
+          <t xml:space="preserve">選んでもらえたのは嬉しいです。でも……みんなで勝ちたかった。次こそは</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[2]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.shy[1]</t>
+          <t xml:space="preserve">defiant.standard.shy[2]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11837,14 +11837,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…。もっと頑張らないと…</t>
+          <t xml:space="preserve">MVP……嬉しいけど、胸を張れない。次は仲間と一緒に笑いたい</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[3]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.shy[2]</t>
+          <t xml:space="preserve">defiant.standard.shy[3]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11869,14 +11869,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱり…わたしなんか…。でも…諦めない…</t>
+          <t xml:space="preserve">こんな賞をもらっても……みんなが悔しい顔してるのに、喜べないです</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.shy[1]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[1]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11901,14 +11901,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…よかった…</t>
+          <t xml:space="preserve">こ、怖かったです。でも……次の相手が来ても、逃げたくなかったんです</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[2]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.shy[2]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[2]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11933,14 +11933,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…終わりじゃないんだ…頑張る</t>
+          <t xml:space="preserve">手が震えてます。でも、最後まで立ててよかった……</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[3]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.shy[1]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[3]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11965,14 +11965,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張れた…かな。もっと強くなりたい…</t>
+          <t xml:space="preserve">何人来るかわからなくて怖かったけど……気づいたら、最後の一人でした</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.shy[2]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11997,14 +11997,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと戦えて…嬉しかった…</t>
+          <t xml:space="preserve">信じられない…。でも…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12029,14 +12029,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">震えてるのは…きっと、嬉しいからだと思う</t>
+          <t xml:space="preserve">わ、わたしが優勝…？ 夢じゃないよね…</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[1]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">postLose.standard.shy[1]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12061,14 +12061,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのが信じられない…でも、負けたくない</t>
+          <t xml:space="preserve">ご、ごめんなさい…。もっと頑張らないと…</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[2]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">postLose.standard.shy[2]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12093,14 +12093,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張する…でも、逃げない</t>
+          <t xml:space="preserve">やっぱり…わたしなんか…。でも…諦めない…</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12125,14 +12125,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張ります…！</t>
+          <t xml:space="preserve">か、勝てた…よかった…</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.shy[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12157,14 +12157,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、私が…？ …頑張らなきゃ</t>
+          <t xml:space="preserve">まだ…終わりじゃないんだ…頑張る</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.shy[2]</t>
+          <t xml:space="preserve">postWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -12189,14 +12189,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、嘘…？ わ、私でいいんですか…？</t>
+          <t xml:space="preserve">が、頑張れた…かな。もっと強くなりたい…</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">postWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12221,14 +12221,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張ります…！</t>
+          <t xml:space="preserve">みんなと戦えて…嬉しかった…</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12253,14 +12253,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…信じられない…夢、みたい…</t>
+          <t xml:space="preserve">震えてるのは…きっと、嬉しいからだと思う</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12285,14 +12285,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…対抗戦を…お願いしたくて…</t>
+          <t xml:space="preserve">ここまで来れたのが信じられない…でも、負けたくない</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12302,12 +12302,12 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12317,14 +12317,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、でも…負けるつもりはないです…</t>
+          <t xml:space="preserve">緊張する…でも、逃げない</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12334,12 +12334,12 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12349,14 +12349,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そ、そうですか…残念です…</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[1]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">summon.standard.shy[1]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12381,14 +12381,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、でも…いつかきっと…</t>
+          <t xml:space="preserve">え、私が…？ …頑張らなきゃ</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[2]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12398,12 +12398,12 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.shy[1]</t>
+          <t xml:space="preserve">summon.standard.shy[2]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12413,14 +12413,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…私が…もっと頑張れていれば…</t>
+          <t xml:space="preserve">う、嘘…？ わ、私でいいんですか…？</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12445,14 +12445,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でも…次こそ…</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12477,14 +12477,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…。みんなのおかげです…</t>
+          <t xml:space="preserve">か、勝てました…信じられない…夢、みたい…</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[1]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12494,12 +12494,12 @@
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12509,14 +12509,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほっとしました…。よかった…</t>
+          <t xml:space="preserve">あ、あの…対抗戦を…お願いしたくて…</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[2]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12541,14 +12541,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…！ み、みんなの看板、汚さずに済んだ…よかった…</t>
+          <t xml:space="preserve">で、でも…負けるつもりはないです…</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[1]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12573,14 +12573,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私でも…団体の役に立てたのかな…</t>
+          <t xml:space="preserve">そ、そうですか…残念です…</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[2]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12590,12 +12590,12 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12605,14 +12605,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、嬉しい…みんなと一緒に戦えて…勝てて…</t>
+          <t xml:space="preserve">で、でも…いつかきっと…</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[1]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12622,29 +12622,29 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.shy[1]</t>
+          <t xml:space="preserve">result_lose.standard.shy[1]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなに幸せなことがあっていいのかな…</t>
+          <t xml:space="preserve">ごめんなさい…私が…もっと頑張れていれば…</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[2]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12654,29 +12654,29 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">result_lose.standard.shy[2]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+          <t xml:space="preserve">悔しい…でも…次こそ…</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[1]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12686,29 +12686,29 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">result_win.standard.shy[1]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+          <t xml:space="preserve">か、勝てた…。みんなのおかげです…</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[2]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12718,59 +12718,283 @@
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">result_win.standard.shy[2]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+          <t xml:space="preserve">ほっとしました…。よかった…</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">か、勝てた…！ み、みんなの看板、汚さずに済んだ…よかった…</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="40" customHeight="1">
+      <c r="A391" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、私でも…団体の役に立てたのかな…</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="40" customHeight="1">
+      <c r="A392" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[3]</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[3]</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う、嬉しい…みんなと一緒に戦えて…勝てて…</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="40" customHeight="1">
+      <c r="A393" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、こんなに幸せなことがあっていいのかな…</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="40" customHeight="1">
+      <c r="A394" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="40" customHeight="1">
+      <c r="A395" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="40" customHeight="1">
+      <c r="A396" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="40" customHeight="1">
+      <c r="A397" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[2]</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr" s="2">
+      <c r="B397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr" s="12">
+      <c r="D397" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr" s="2">
+      <c r="E397" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr" s="3">
+      <c r="F397" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H390"/>
+  <autoFilter ref="A1:H397"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×内気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H390"/>
+  <dimension ref="A1:H392"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10756,7 +10756,7 @@
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.shy[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.shy[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.shy[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10781,14 +10781,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、えっと…もう少し頑張ります…</t>
+          <t xml:space="preserve">怖い…でも…負けたくない…</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.shy[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.shy[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.shy[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10813,14 +10813,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の練習…うまくできてるかな…</t>
+          <t xml:space="preserve">あの子がいると思うと、うまく練習できなくて…</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.shy[1]</t>
+          <t xml:space="preserve">GL-02.standard.shy[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10845,14 +10845,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私…ちゃんとやれてますか…？ 不安です…</t>
+          <t xml:space="preserve">あ、えっと…もう少し頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.shy[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.shy[1]</t>
+          <t xml:space="preserve">GL-02.standard.shy[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10877,14 +10877,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…ここにいていいんですね…嬉しいです…</t>
+          <t xml:space="preserve">今日の練習…うまくできてるかな…</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.shy[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.shy[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.shy[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10909,14 +10909,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">近くにいてくれると…安心する…</t>
+          <t xml:space="preserve">私…ちゃんとやれてますか…？ 不安です…</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.shy[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.shy[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.shy[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10941,14 +10941,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すごいな…私も頑張らなきゃ…</t>
+          <t xml:space="preserve">あ、あの…ここにいていいんですね…嬉しいです…</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.shy[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.shy[1]</t>
+          <t xml:space="preserve">GL-04.standard.shy[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10973,14 +10973,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出られなかった…私じゃダメなんですか…</t>
+          <t xml:space="preserve">近くにいてくれると…安心する…</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.shy[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.shy[2]</t>
+          <t xml:space="preserve">GL-05.standard.shy[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11005,14 +11005,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…次は…出してもらえますか…？</t>
+          <t xml:space="preserve">…すごいな…私も頑張らなきゃ…</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.shy[1]</t>
+          <t xml:space="preserve">GL-06.standard.shy[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11037,14 +11037,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が…重くて…すみません…迷惑かけて…</t>
+          <t xml:space="preserve">出られなかった…私じゃダメなんですか…</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.shy[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.shy[1]</t>
+          <t xml:space="preserve">GL-06.standard.shy[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11069,14 +11069,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私…足引っ張ってますよね…ごめんなさい…</t>
+          <t xml:space="preserve">あの…次は…出してもらえますか…？</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.shy[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.shy[2]</t>
+          <t xml:space="preserve">GL-07.standard.shy[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11101,14 +11101,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てない…勝てない…どうしたらいいの…</t>
+          <t xml:space="preserve">体が…重くて…すみません…迷惑かけて…</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.shy[1]</t>
+          <t xml:space="preserve">GL-08.standard.shy[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11133,14 +11133,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝…嘘みたい…でも自信になってます…！</t>
+          <t xml:space="preserve">わ、私…足引っ張ってますよね…ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.shy[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.shy[1]</t>
+          <t xml:space="preserve">GL-08.standard.shy[2]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11165,14 +11165,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなに置いてかれちゃう…怖い…</t>
+          <t xml:space="preserve">勝てない…勝てない…どうしたらいいの…</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.shy[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.shy[2]</t>
+          <t xml:space="preserve">GL-09.standard.shy[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11197,14 +11197,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我…早く治って…お願い…</t>
+          <t xml:space="preserve">連勝…嘘みたい…でも自信になってます…！</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">GL-10.standard.shy[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11229,14 +11229,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ…なんか、普通に戻っちゃった…かな</t>
+          <t xml:space="preserve">みんなに置いてかれちゃう…怖い…</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.shy[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">GL-10.standard.shy[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11261,14 +11261,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すごく調子よかったのに…でも、いい思い出です…</t>
+          <t xml:space="preserve">怪我…早く治って…お願い…</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11278,29 +11278,29 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたなんて…。身体は痛いけど、最後まで、逃げたくない</t>
+          <t xml:space="preserve">あ…なんか、普通に戻っちゃった…かな</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11310,29 +11310,29 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…。でも、みんなが繋いでくれたから、私が締めなきゃ</t>
+          <t xml:space="preserve">すごく調子よかったのに…でも、いい思い出です…</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11357,14 +11357,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、相手が来る…。怖い、けど…ここで逃げたら、繋げないから</t>
+          <t xml:space="preserve">ここまで来られたなんて…。身体は痛いけど、最後まで、逃げたくない</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11389,14 +11389,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…でも、私の番だから。行かなきゃ</t>
+          <t xml:space="preserve">足が震えてる…。でも、みんなが繋いでくれたから、私が締めなきゃ</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.shy[1]</t>
+          <t xml:space="preserve">preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11421,14 +11421,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人…倒せた…！ はぁ、はぁ…怖いけど、まだ退かない…！ 次の人、来て…！</t>
+          <t xml:space="preserve">あ、相手が来る…。怖い、けど…ここで逃げたら、繋げないから</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.shy[2]</t>
+          <t xml:space="preserve">preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11453,14 +11453,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足が震えてる…でも、まだ立ってる。ここは、渡せないから…次、来て</t>
+          <t xml:space="preserve">足が震えてる…でも、私の番だから。行かなきゃ</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">survivor.standard.shy[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11485,14 +11485,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私がMVPでいいのかな……でも、二人がつないでくれたから、ここに立てました</t>
+          <t xml:space="preserve">一人…倒せた…！ はぁ、はぁ…怖いけど、まだ退かない…！ 次の人、来て…！</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.shy[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[2]</t>
+          <t xml:space="preserve">survivor.standard.shy[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11517,14 +11517,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">み、みんなで勝てて……ほんとに嬉しい。私なんかがここに立ってていいのかな</t>
+          <t xml:space="preserve">足が震えてる…でも、まだ立ってる。ここは、渡せないから…次、来て</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[3]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11549,14 +11549,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てたこと、それが一番嬉しいです。MVPは……二人のおかげです</t>
+          <t xml:space="preserve">わ、私がMVPでいいのかな……でも、二人がつないでくれたから、ここに立てました</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11581,14 +11581,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでもらえたのは嬉しいです。でも……みんなで勝ちたかった。次こそは</t>
+          <t xml:space="preserve">み、みんなで勝てて……ほんとに嬉しい。私なんかがここに立ってていいのかな</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.shy[3]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[2]</t>
+          <t xml:space="preserve">champion.standard.shy[3]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11613,14 +11613,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP……嬉しいけど、胸を張れない。次は仲間と一緒に笑いたい</t>
+          <t xml:space="preserve">三人で勝てたこと、それが一番嬉しいです。MVPは……二人のおかげです</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.shy[3]</t>
+          <t xml:space="preserve">defiant.standard.shy[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11645,14 +11645,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな賞をもらっても……みんなが悔しい顔してるのに、喜べないです</t>
+          <t xml:space="preserve">選んでもらえたのは嬉しいです。でも……みんなで勝ちたかった。次こそは</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[2]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[1]</t>
+          <t xml:space="preserve">defiant.standard.shy[2]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11677,14 +11677,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、怖かったです。でも……次の相手が来ても、逃げたくなかったんです</t>
+          <t xml:space="preserve">MVP……嬉しいけど、胸を張れない。次は仲間と一緒に笑いたい</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.shy[3]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[2]</t>
+          <t xml:space="preserve">defiant.standard.shy[3]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11709,14 +11709,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">手が震えてます。でも、最後まで立ててよかった……</t>
+          <t xml:space="preserve">こんな賞をもらっても……みんなが悔しい顔してるのに、喜べないです</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.shy[3]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11741,14 +11741,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来るかわからなくて怖かったけど……気づいたら、最後の一人でした</t>
+          <t xml:space="preserve">こ、怖かったです。でも……次の相手が来ても、逃げたくなかったんです</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[2]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[1]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[2]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11773,14 +11773,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じられない…。でも…嬉しい…！</t>
+          <t xml:space="preserve">手が震えてます。でも、最後まで立ててよかった……</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.shy[3]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11790,12 +11790,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.shy[2]</t>
+          <t xml:space="preserve">gauntlet.standard.shy[3]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11805,14 +11805,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしが優勝…？ 夢じゃないよね…</t>
+          <t xml:space="preserve">何人来るかわからなくて怖かったけど……気づいたら、最後の一人でした</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.shy[1]</t>
+          <t xml:space="preserve">champion.standard.shy[1]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11837,14 +11837,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご、ごめんなさい…。もっと頑張らないと…</t>
+          <t xml:space="preserve">信じられない…。でも…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.shy[2]</t>
+          <t xml:space="preserve">champion.standard.shy[2]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11869,14 +11869,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱり…わたしなんか…。でも…諦めない…</t>
+          <t xml:space="preserve">わ、わたしが優勝…？ 夢じゃないよね…</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.shy[1]</t>
+          <t xml:space="preserve">postLose.standard.shy[1]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11901,14 +11901,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…よかった…</t>
+          <t xml:space="preserve">ご、ごめんなさい…。もっと頑張らないと…</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.shy[2]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.shy[2]</t>
+          <t xml:space="preserve">postLose.standard.shy[2]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11933,14 +11933,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…終わりじゃないんだ…頑張る</t>
+          <t xml:space="preserve">やっぱり…わたしなんか…。でも…諦めない…</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.shy[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11965,14 +11965,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張れた…かな。もっと強くなりたい…</t>
+          <t xml:space="preserve">か、勝てた…よかった…</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.shy[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11997,14 +11997,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと戦えて…嬉しかった…</t>
+          <t xml:space="preserve">まだ…終わりじゃないんだ…頑張る</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[1]</t>
+          <t xml:space="preserve">postWin.standard.shy[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12029,14 +12029,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">震えてるのは…きっと、嬉しいからだと思う</t>
+          <t xml:space="preserve">が、頑張れた…かな。もっと強くなりたい…</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.shy[2]</t>
+          <t xml:space="preserve">postWin.standard.shy[2]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12061,14 +12061,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのが信じられない…でも、負けたくない</t>
+          <t xml:space="preserve">みんなと戦えて…嬉しかった…</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[1]</t>
+          <t xml:space="preserve">preFinal.standard.shy[1]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12093,14 +12093,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張する…でも、逃げない</t>
+          <t xml:space="preserve">震えてるのは…きっと、嬉しいからだと思う</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.shy[2]</t>
+          <t xml:space="preserve">preFinal.standard.shy[2]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12125,14 +12125,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張ります…！</t>
+          <t xml:space="preserve">ここまで来れたのが信じられない…でも、負けたくない</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.shy[1]</t>
+          <t xml:space="preserve">preMatch.standard.shy[1]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12157,14 +12157,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、私が…？ …頑張らなきゃ</t>
+          <t xml:space="preserve">緊張する…でも、逃げない</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.shy[2]</t>
+          <t xml:space="preserve">preMatch.standard.shy[2]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -12189,14 +12189,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、嘘…？ わ、私でいいんですか…？</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">summon.standard.shy[1]</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12221,14 +12221,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張ります…！</t>
+          <t xml:space="preserve">え、私が…？ …頑張らなきゃ</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.shy[2]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">summon.standard.shy[2]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12253,14 +12253,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てました…信じられない…夢、みたい…</t>
+          <t xml:space="preserve">う、嘘…？ わ、私でいいんですか…？</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="12">
@@ -12285,14 +12285,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…対抗戦を…お願いしたくて…</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12302,12 +12302,12 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12317,14 +12317,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、でも…負けるつもりはないです…</t>
+          <t xml:space="preserve">か、勝てました…信じられない…夢、みたい…</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[1]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
@@ -12349,14 +12349,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そ、そうですか…残念です…</t>
+          <t xml:space="preserve">あ、あの…対抗戦を…お願いしたくて…</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.shy[2]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
@@ -12381,14 +12381,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">で、でも…いつかきっと…</t>
+          <t xml:space="preserve">で、でも…負けるつもりはないです…</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[1]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12398,12 +12398,12 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12413,14 +12413,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…私が…もっと頑張れていれば…</t>
+          <t xml:space="preserve">そ、そうですか…残念です…</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.shy[2]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.shy[2]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12445,14 +12445,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でも…次こそ…</t>
+          <t xml:space="preserve">で、でも…いつかきっと…</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.shy[1]</t>
+          <t xml:space="preserve">result_lose.standard.shy[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12477,14 +12477,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…。みんなのおかげです…</t>
+          <t xml:space="preserve">ごめんなさい…私が…もっと頑張れていれば…</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.shy[2]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.shy[2]</t>
+          <t xml:space="preserve">result_lose.standard.shy[2]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12509,14 +12509,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほっとしました…。よかった…</t>
+          <t xml:space="preserve">悔しい…でも…次こそ…</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">result_win.standard.shy[1]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12541,14 +12541,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">か、勝てた…！ み、みんなの看板、汚さずに済んだ…よかった…</t>
+          <t xml:space="preserve">か、勝てた…。みんなのおかげです…</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.shy[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12558,12 +12558,12 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">result_win.standard.shy[2]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12573,14 +12573,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、私でも…団体の役に立てたのかな…</t>
+          <t xml:space="preserve">ほっとしました…。よかった…</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[3]</t>
+          <t xml:space="preserve">standard.shy[1]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12605,14 +12605,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、嬉しい…みんなと一緒に戦えて…勝てて…</t>
+          <t xml:space="preserve">か、勝てた…！ み、みんなの看板、汚さずに済んだ…よかった…</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[2]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12622,29 +12622,29 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんなに幸せなことがあっていいのかな…</t>
+          <t xml:space="preserve">わ、私でも…団体の役に立てたのかな…</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.shy[3]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12654,29 +12654,29 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[1]</t>
+          <t xml:space="preserve">standard.shy[3]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+          <t xml:space="preserve">う、嬉しい…みんなと一緒に戦えて…勝てて…</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.shy[1]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12686,29 +12686,29 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.shy[2]</t>
+          <t xml:space="preserve">fighter.standard.shy[1]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+          <t xml:space="preserve">こ、こんなに幸せなことがあっていいのかな…</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[1]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="12">
@@ -12733,44 +12733,108 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[2]</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="40" customHeight="1">
+      <c r="A391" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.shy[1]</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="40" customHeight="1">
+      <c r="A392" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.shy[2]</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr" s="2">
+      <c r="B392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr" s="12">
+      <c r="D392" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.shy[2]</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr" s="2">
+      <c r="E392" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr" s="3">
+      <c r="F392" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H390"/>
+  <autoFilter ref="A1:H392"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×内気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×内気.xlsx
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言うか迷ったんですけど……あの人と、やりたいです。</t>
+          <t xml:space="preserve">言うか迷ったんですけど……三人で、あちらへ行きたいです。</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わがままですよね。……でも、どうしても。</t>
+          <t xml:space="preserve">三人で行きたいんです。わがままですよね。……でも、どうしても。</t>
         </is>
       </c>
     </row>
